--- a/Finance System.xlsx
+++ b/Finance System.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2025_DigiLivo\GERENTE DE PROYECTOS\Proyecto Choriboni\Base Total_Choriboni Parrilla\Sucursarl_Choriboni\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Fabrica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5132DD-39CC-4BDF-9139-25660C9222FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="763" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="749" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="maestro" sheetId="48" r:id="rId1"/>
@@ -58,10 +57,10 @@
     <definedName name="SegmentaciónDeDatos_Tipo_día">#N/A</definedName>
     <definedName name="Stock_Inventario">[1]!Inventario_SICOV2[#Data]</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId26"/>
-    <pivotCache cacheId="1" r:id="rId27"/>
+    <pivotCache cacheId="6" r:id="rId26"/>
+    <pivotCache cacheId="7" r:id="rId27"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -92,12 +91,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Usuario</author>
   </authors>
   <commentList>
-    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="D35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -116,12 +115,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Usuario</author>
   </authors>
   <commentList>
-    <comment ref="V17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000001000000}">
+    <comment ref="V17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000002000000}">
+    <comment ref="A21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -160,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000003000000}">
+    <comment ref="C31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -184,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000004000000}">
+    <comment ref="D31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -208,7 +207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000005000000}">
+    <comment ref="C32" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -238,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="442">
   <si>
     <t>Mes</t>
   </si>
@@ -1549,11 +1548,47 @@
   <si>
     <t>coca cola</t>
   </si>
+  <si>
+    <t>Coca cola</t>
+  </si>
+  <si>
+    <t>Postobon</t>
+  </si>
+  <si>
+    <t>Chori- CRUDO</t>
+  </si>
+  <si>
+    <t>parri tres carnes</t>
+  </si>
+  <si>
+    <t>carne + chorizo</t>
+  </si>
+  <si>
+    <t>tinto</t>
+  </si>
+  <si>
+    <t>Hit</t>
+  </si>
+  <si>
+    <t>parri 48</t>
+  </si>
+  <si>
+    <t>parri 70</t>
+  </si>
+  <si>
+    <t>parri 40</t>
+  </si>
+  <si>
+    <t>costo_producto</t>
+  </si>
+  <si>
+    <t>precio_producto</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="15">
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -2596,7 +2631,7 @@
     <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="278">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3105,6 +3140,12 @@
     <xf numFmtId="14" fontId="21" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="31" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="36" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="31" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3135,335 +3176,23 @@
     <cellStyle name="Incorrecto" xfId="17" builtinId="27"/>
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
     <cellStyle name="Millares [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Millares 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Millares 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Millares 3 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Millares 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Millares 4 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Millares 2" xfId="7"/>
+    <cellStyle name="Millares 3" xfId="9"/>
+    <cellStyle name="Millares 3 2" xfId="15"/>
+    <cellStyle name="Millares 4" xfId="13"/>
+    <cellStyle name="Millares 4 2" xfId="14"/>
     <cellStyle name="Moneda" xfId="4" builtinId="4"/>
-    <cellStyle name="Moneda 2" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Moneda 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Moneda 2" xfId="5"/>
+    <cellStyle name="Moneda 3" xfId="12"/>
     <cellStyle name="Neutral" xfId="18" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="6" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Normal 3" xfId="10" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Normal 5" xfId="8" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal 2" xfId="6"/>
+    <cellStyle name="Normal 3" xfId="10"/>
+    <cellStyle name="Normal 5" xfId="8"/>
     <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Porcentaje 2" xfId="11"/>
   </cellStyles>
   <dxfs count="295">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Tw Cen MT"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="175" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="5" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="5" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="5" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4192,6 +3921,146 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5571,6 +5440,141 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="174" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     </dxf>
     <dxf>
@@ -5616,15 +5620,6 @@
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
@@ -6667,6 +6662,34 @@
       <numFmt numFmtId="175" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Tw Cen MT"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="175" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
     </dxf>
     <dxf>
@@ -6697,6 +6720,23 @@
         <name val="Tw Cen MT"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCCCFF"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -6807,7 +6847,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6829,6 +6869,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -6865,7 +6906,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -7273,6 +7316,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -7715,6 +7759,7 @@
         <c:dispUnits>
           <c:custUnit val="1000"/>
           <c:dispUnitsLbl>
+            <c:layout/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -7896,7 +7941,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7972,47 +8017,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CO"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -8475,6 +8479,7 @@
         <c:dispUnits>
           <c:custUnit val="1000"/>
           <c:dispUnitsLbl>
+            <c:layout/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -11499,10 +11504,24 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{6681B32D-2E24-4636-A78F-BC926B879589}" type="pres">
       <dgm:prSet presAssocID="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" presName="centerShape" presStyleLbl="node0" presStyleIdx="0" presStyleCnt="1" custScaleX="203757" custScaleY="202114" custLinFactNeighborX="1861" custLinFactNeighborY="-475"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{774A2DE8-AFF6-46FF-A0E0-2F858C500C72}" type="pres">
       <dgm:prSet presAssocID="{8D7DD220-F386-442E-B845-EF7E1C904A2A}" presName="node" presStyleLbl="node1" presStyleIdx="0" presStyleCnt="4">
@@ -11511,6 +11530,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{89EF00DB-84CB-4DF7-BCA2-471101864F45}" type="pres">
       <dgm:prSet presAssocID="{8D7DD220-F386-442E-B845-EF7E1C904A2A}" presName="dummy" presStyleCnt="0"/>
@@ -11519,6 +11545,13 @@
     <dgm:pt modelId="{8E4E5F5A-A4FE-41A6-A500-323272351F28}" type="pres">
       <dgm:prSet presAssocID="{334CC921-6B35-4CF4-B9A8-2E0597CA35AC}" presName="sibTrans" presStyleLbl="sibTrans2D1" presStyleIdx="0" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{EF7C0C61-9105-4366-A3B0-0C5E966BDBC2}" type="pres">
       <dgm:prSet presAssocID="{CE51C380-F842-45A4-9BFE-9CFC45519591}" presName="node" presStyleLbl="node1" presStyleIdx="1" presStyleCnt="4">
@@ -11527,6 +11560,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{156ECFEF-2E35-4003-A7FA-5DFA938E1B9A}" type="pres">
       <dgm:prSet presAssocID="{CE51C380-F842-45A4-9BFE-9CFC45519591}" presName="dummy" presStyleCnt="0"/>
@@ -11535,6 +11575,13 @@
     <dgm:pt modelId="{4BE38136-E3AF-4B08-B25A-EF0717CE08AC}" type="pres">
       <dgm:prSet presAssocID="{D6539722-A427-4279-AAFE-BCE6254C8B6D}" presName="sibTrans" presStyleLbl="sibTrans2D1" presStyleIdx="1" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{DDE904DE-5D6B-417D-9107-C760ED08BAD2}" type="pres">
       <dgm:prSet presAssocID="{67F7EEAB-2580-4068-AF5C-629485D93C71}" presName="node" presStyleLbl="node1" presStyleIdx="2" presStyleCnt="4">
@@ -11543,6 +11590,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{315A78A8-C95C-40CA-AD6C-735C8D4F8751}" type="pres">
       <dgm:prSet presAssocID="{67F7EEAB-2580-4068-AF5C-629485D93C71}" presName="dummy" presStyleCnt="0"/>
@@ -11551,6 +11605,13 @@
     <dgm:pt modelId="{8D38B28F-2BC1-40FA-96A2-DE28DAAC0DA3}" type="pres">
       <dgm:prSet presAssocID="{D25BFE8D-A868-4653-A189-D9BA8E0A0112}" presName="sibTrans" presStyleLbl="sibTrans2D1" presStyleIdx="2" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{D695B8B3-A625-4533-8B71-F37199DAACE0}" type="pres">
       <dgm:prSet presAssocID="{81F63DCC-F876-4F38-B52D-11783D37F89B}" presName="node" presStyleLbl="node1" presStyleIdx="3" presStyleCnt="4">
@@ -11559,6 +11620,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{545EC8BD-84CD-4158-AF64-19FED48EFBA6}" type="pres">
       <dgm:prSet presAssocID="{81F63DCC-F876-4F38-B52D-11783D37F89B}" presName="dummy" presStyleCnt="0"/>
@@ -11567,22 +11635,29 @@
     <dgm:pt modelId="{20B6ADC2-378A-4BF9-BACC-23B1CC38C95D}" type="pres">
       <dgm:prSet presAssocID="{6035BF3A-C2CA-4EA8-9FAA-BADEDD2EAED4}" presName="sibTrans" presStyleLbl="sibTrans2D1" presStyleIdx="3" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
   </dgm:ptLst>
   <dgm:cxnLst>
+    <dgm:cxn modelId="{47406005-90A9-4C79-881A-13F5BE15AF74}" srcId="{64B47852-742A-46CD-B1B7-548D32462E75}" destId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" srcOrd="0" destOrd="0" parTransId="{B1DF4A96-3EC7-4BBD-89F1-AD7C14A81899}" sibTransId="{3EEC6871-EAA1-4B12-92F5-78BBF2682B80}"/>
     <dgm:cxn modelId="{5C181302-80C8-4752-A512-8668D647B9D1}" type="presOf" srcId="{CE51C380-F842-45A4-9BFE-9CFC45519591}" destId="{EF7C0C61-9105-4366-A3B0-0C5E966BDBC2}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
-    <dgm:cxn modelId="{47406005-90A9-4C79-881A-13F5BE15AF74}" srcId="{64B47852-742A-46CD-B1B7-548D32462E75}" destId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" srcOrd="0" destOrd="0" parTransId="{B1DF4A96-3EC7-4BBD-89F1-AD7C14A81899}" sibTransId="{3EEC6871-EAA1-4B12-92F5-78BBF2682B80}"/>
-    <dgm:cxn modelId="{D8ED910E-849A-417F-9DFD-CA4E2D793CB2}" srcId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" destId="{8D7DD220-F386-442E-B845-EF7E1C904A2A}" srcOrd="0" destOrd="0" parTransId="{6037A481-3449-44A4-A4FB-792EC8338FC2}" sibTransId="{334CC921-6B35-4CF4-B9A8-2E0597CA35AC}"/>
+    <dgm:cxn modelId="{8A0EFC57-49F7-4635-AC30-320B0F3DCF36}" type="presOf" srcId="{81F63DCC-F876-4F38-B52D-11783D37F89B}" destId="{D695B8B3-A625-4533-8B71-F37199DAACE0}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
+    <dgm:cxn modelId="{F8121723-0809-48DA-BF80-BCF0910624A6}" type="presOf" srcId="{8D7DD220-F386-442E-B845-EF7E1C904A2A}" destId="{774A2DE8-AFF6-46FF-A0E0-2F858C500C72}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
     <dgm:cxn modelId="{03E07817-2B7B-4081-AB9C-F6AF32DB5746}" type="presOf" srcId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" destId="{6681B32D-2E24-4636-A78F-BC926B879589}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
+    <dgm:cxn modelId="{7FD81B1C-7895-4194-A2A3-800507B758AD}" type="presOf" srcId="{67F7EEAB-2580-4068-AF5C-629485D93C71}" destId="{DDE904DE-5D6B-417D-9107-C760ED08BAD2}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
     <dgm:cxn modelId="{4BB7A61B-472C-4BC5-A509-E0EBA6F220FD}" type="presOf" srcId="{334CC921-6B35-4CF4-B9A8-2E0597CA35AC}" destId="{8E4E5F5A-A4FE-41A6-A500-323272351F28}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
-    <dgm:cxn modelId="{7FD81B1C-7895-4194-A2A3-800507B758AD}" type="presOf" srcId="{67F7EEAB-2580-4068-AF5C-629485D93C71}" destId="{DDE904DE-5D6B-417D-9107-C760ED08BAD2}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
-    <dgm:cxn modelId="{F8121723-0809-48DA-BF80-BCF0910624A6}" type="presOf" srcId="{8D7DD220-F386-442E-B845-EF7E1C904A2A}" destId="{774A2DE8-AFF6-46FF-A0E0-2F858C500C72}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
-    <dgm:cxn modelId="{294BD22B-42E3-43A2-B7D3-AAE0EB9F08EC}" type="presOf" srcId="{D6539722-A427-4279-AAFE-BCE6254C8B6D}" destId="{4BE38136-E3AF-4B08-B25A-EF0717CE08AC}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
+    <dgm:cxn modelId="{F3EDA979-EC2E-4E52-B0D5-975D1C5CF72E}" srcId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" destId="{CE51C380-F842-45A4-9BFE-9CFC45519591}" srcOrd="1" destOrd="0" parTransId="{E61CCCE9-E0CC-43AD-A85A-9E61151C2186}" sibTransId="{D6539722-A427-4279-AAFE-BCE6254C8B6D}"/>
     <dgm:cxn modelId="{42A4B75B-9768-4FC0-BA45-DDECAA618095}" srcId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" destId="{81F63DCC-F876-4F38-B52D-11783D37F89B}" srcOrd="3" destOrd="0" parTransId="{D198EFAD-0048-4B20-B3C3-3F23D58C816B}" sibTransId="{6035BF3A-C2CA-4EA8-9FAA-BADEDD2EAED4}"/>
     <dgm:cxn modelId="{B6EA4463-6623-4E17-975C-985A10B889EC}" type="presOf" srcId="{64B47852-742A-46CD-B1B7-548D32462E75}" destId="{75EE6453-57B8-4606-8819-88881D637227}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
     <dgm:cxn modelId="{11A9E467-3C1C-4D2E-9C32-1557266CDC85}" type="presOf" srcId="{D25BFE8D-A868-4653-A189-D9BA8E0A0112}" destId="{8D38B28F-2BC1-40FA-96A2-DE28DAAC0DA3}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
-    <dgm:cxn modelId="{8A0EFC57-49F7-4635-AC30-320B0F3DCF36}" type="presOf" srcId="{81F63DCC-F876-4F38-B52D-11783D37F89B}" destId="{D695B8B3-A625-4533-8B71-F37199DAACE0}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
-    <dgm:cxn modelId="{F3EDA979-EC2E-4E52-B0D5-975D1C5CF72E}" srcId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" destId="{CE51C380-F842-45A4-9BFE-9CFC45519591}" srcOrd="1" destOrd="0" parTransId="{E61CCCE9-E0CC-43AD-A85A-9E61151C2186}" sibTransId="{D6539722-A427-4279-AAFE-BCE6254C8B6D}"/>
+    <dgm:cxn modelId="{294BD22B-42E3-43A2-B7D3-AAE0EB9F08EC}" type="presOf" srcId="{D6539722-A427-4279-AAFE-BCE6254C8B6D}" destId="{4BE38136-E3AF-4B08-B25A-EF0717CE08AC}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
+    <dgm:cxn modelId="{D8ED910E-849A-417F-9DFD-CA4E2D793CB2}" srcId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" destId="{8D7DD220-F386-442E-B845-EF7E1C904A2A}" srcOrd="0" destOrd="0" parTransId="{6037A481-3449-44A4-A4FB-792EC8338FC2}" sibTransId="{334CC921-6B35-4CF4-B9A8-2E0597CA35AC}"/>
     <dgm:cxn modelId="{D3DFB9C3-CA66-45B9-A86C-279C13D83A06}" type="presOf" srcId="{6035BF3A-C2CA-4EA8-9FAA-BADEDD2EAED4}" destId="{20B6ADC2-378A-4BF9-BACC-23B1CC38C95D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
     <dgm:cxn modelId="{ECEC49F8-D581-4133-AA50-BE4F863DCA95}" srcId="{6E7D1AF1-DCBD-479A-8F21-3212D60D2F78}" destId="{67F7EEAB-2580-4068-AF5C-629485D93C71}" srcOrd="2" destOrd="0" parTransId="{C561CAB8-224F-4F98-A097-6518D165B2FA}" sibTransId="{D25BFE8D-A868-4653-A189-D9BA8E0A0112}"/>
     <dgm:cxn modelId="{1110A21B-F48F-4DFA-8C34-CEFC922A0C63}" type="presParOf" srcId="{75EE6453-57B8-4606-8819-88881D637227}" destId="{6681B32D-2E24-4636-A78F-BC926B879589}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/radial6"/>
@@ -12030,6 +12105,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{E47C858A-1874-4624-871F-0FF6CF740EFD}" type="pres">
       <dgm:prSet presAssocID="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" presName="root1" presStyleCnt="0"/>
@@ -12042,6 +12124,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{6D5C6819-F805-4502-B02D-B89F900D7C7C}" type="pres">
       <dgm:prSet presAssocID="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" presName="level2hierChild" presStyleCnt="0"/>
@@ -12050,10 +12139,24 @@
     <dgm:pt modelId="{1E4F17B2-61C1-4211-9112-21EAEF2D66DE}" type="pres">
       <dgm:prSet presAssocID="{1A01BAB7-D852-42EC-A523-3E0FC524173A}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="2"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{A6B5AC58-8480-4DD8-9BC5-CDFC9B0E3773}" type="pres">
       <dgm:prSet presAssocID="{1A01BAB7-D852-42EC-A523-3E0FC524173A}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="2"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{EDD66041-8B16-45B0-BD32-E81D4E90949B}" type="pres">
       <dgm:prSet presAssocID="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" presName="root2" presStyleCnt="0"/>
@@ -12066,6 +12169,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{5318A4DA-010F-47AA-AC66-AE8EDE3DA503}" type="pres">
       <dgm:prSet presAssocID="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12074,10 +12184,24 @@
     <dgm:pt modelId="{FA110F8D-A383-48E7-9886-D97D3E84D77B}" type="pres">
       <dgm:prSet presAssocID="{36864AED-CFD1-4B11-9E77-829B0A685D8C}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="3"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{1199E3A4-F43D-4B8D-9B92-9CCFF81D35F7}" type="pres">
       <dgm:prSet presAssocID="{36864AED-CFD1-4B11-9E77-829B0A685D8C}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="3"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{C6DF0779-43DD-4B1E-A772-03F744E8787F}" type="pres">
       <dgm:prSet presAssocID="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" presName="root2" presStyleCnt="0"/>
@@ -12090,6 +12214,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{A55A60E8-CF45-462B-BE7D-C8E7CDACE2A1}" type="pres">
       <dgm:prSet presAssocID="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12098,10 +12229,24 @@
     <dgm:pt modelId="{D74353A1-7855-41D7-BD9C-12C9D6E144B7}" type="pres">
       <dgm:prSet presAssocID="{9082B496-25FE-4169-9363-EAD41C1BAD0D}" presName="conn2-1" presStyleLbl="parChTrans1D4" presStyleIdx="0" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{D3A862F4-77FC-4D64-8A8A-38BAB036F2ED}" type="pres">
       <dgm:prSet presAssocID="{9082B496-25FE-4169-9363-EAD41C1BAD0D}" presName="connTx" presStyleLbl="parChTrans1D4" presStyleIdx="0" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{772AE574-E155-41C1-8C7C-53A0CA8E64A6}" type="pres">
       <dgm:prSet presAssocID="{C5672A87-218B-4E36-BC10-7ABBD4A208F8}" presName="root2" presStyleCnt="0"/>
@@ -12114,6 +12259,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{320C7F01-7E38-48B3-A10C-3FC555DC5913}" type="pres">
       <dgm:prSet presAssocID="{C5672A87-218B-4E36-BC10-7ABBD4A208F8}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12122,10 +12274,24 @@
     <dgm:pt modelId="{D513FF87-3C30-4322-BFFA-C63F22E86710}" type="pres">
       <dgm:prSet presAssocID="{1C0ECF78-B8D5-495F-8B34-81D90F573DFC}" presName="conn2-1" presStyleLbl="parChTrans1D4" presStyleIdx="1" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{993821BC-5B4C-4351-A21C-51C3F561216C}" type="pres">
       <dgm:prSet presAssocID="{1C0ECF78-B8D5-495F-8B34-81D90F573DFC}" presName="connTx" presStyleLbl="parChTrans1D4" presStyleIdx="1" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{383A2893-2927-46FD-8384-993B43F7969D}" type="pres">
       <dgm:prSet presAssocID="{C9B97DA7-12E3-4241-8F63-104B4ECBB5A4}" presName="root2" presStyleCnt="0"/>
@@ -12138,6 +12304,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{780A8359-8C36-45E9-A964-1C3E88BE545D}" type="pres">
       <dgm:prSet presAssocID="{C9B97DA7-12E3-4241-8F63-104B4ECBB5A4}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12146,10 +12319,24 @@
     <dgm:pt modelId="{B8B595D4-1AA7-4313-8314-007ECD9CDB77}" type="pres">
       <dgm:prSet presAssocID="{55C1839A-3EE2-469A-A968-C59B499D05BA}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="3"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{B1487175-814D-407C-8DA0-5AF7332CCA9C}" type="pres">
       <dgm:prSet presAssocID="{55C1839A-3EE2-469A-A968-C59B499D05BA}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="3"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{1357D8B1-ABAA-4F0E-9964-63439D698976}" type="pres">
       <dgm:prSet presAssocID="{0914DEFE-6C17-444F-A152-4ADFA2A76D26}" presName="root2" presStyleCnt="0"/>
@@ -12162,6 +12349,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{F9C45E20-25D5-4575-97DD-06CA105F6671}" type="pres">
       <dgm:prSet presAssocID="{0914DEFE-6C17-444F-A152-4ADFA2A76D26}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12170,10 +12364,24 @@
     <dgm:pt modelId="{C2813F44-1BCE-4CF0-A191-6A9BA88049E6}" type="pres">
       <dgm:prSet presAssocID="{E4A990BC-AF9F-4844-9083-823B3AD7C5C2}" presName="conn2-1" presStyleLbl="parChTrans1D4" presStyleIdx="2" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{AD1E0002-1710-4BA8-9A2D-4BE914CC023A}" type="pres">
       <dgm:prSet presAssocID="{E4A990BC-AF9F-4844-9083-823B3AD7C5C2}" presName="connTx" presStyleLbl="parChTrans1D4" presStyleIdx="2" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{25551B56-AC69-4956-82A8-51CEF5CB5FFD}" type="pres">
       <dgm:prSet presAssocID="{31D6180F-ECE4-4AAC-88E5-C9AF6894F914}" presName="root2" presStyleCnt="0"/>
@@ -12186,6 +12394,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{FF76B8D6-FA6D-40E5-876A-C0DE88BB6E8E}" type="pres">
       <dgm:prSet presAssocID="{31D6180F-ECE4-4AAC-88E5-C9AF6894F914}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12194,10 +12409,24 @@
     <dgm:pt modelId="{4BC60D47-C429-461D-86FB-7B0D10F0C78D}" type="pres">
       <dgm:prSet presAssocID="{A025D5F7-5B4B-4020-AB63-5C964A5C6026}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="2"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{EFA5B1EC-EF2F-43C8-B9F3-3110BC769A18}" type="pres">
       <dgm:prSet presAssocID="{A025D5F7-5B4B-4020-AB63-5C964A5C6026}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="2"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{64146AE4-9575-4B5F-86EE-E34D589A3291}" type="pres">
       <dgm:prSet presAssocID="{C6A1D183-7FF4-4FAE-B98F-BC54AB628D5A}" presName="root2" presStyleCnt="0"/>
@@ -12210,6 +12439,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{A22358CE-1CCE-4B61-969C-1701235FD7DB}" type="pres">
       <dgm:prSet presAssocID="{C6A1D183-7FF4-4FAE-B98F-BC54AB628D5A}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12218,10 +12454,24 @@
     <dgm:pt modelId="{D6282B98-BD3A-41BF-943D-112DAAE6E3D3}" type="pres">
       <dgm:prSet presAssocID="{B04B3A0E-FD10-45FE-A5E2-BCCFAF03BAF1}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="3"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{B7C4DFC0-44F7-47C9-A480-3B14710B7086}" type="pres">
       <dgm:prSet presAssocID="{B04B3A0E-FD10-45FE-A5E2-BCCFAF03BAF1}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="3"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{7E6115F4-A77F-4828-BD14-908B1440F00B}" type="pres">
       <dgm:prSet presAssocID="{8B7301AD-5D0D-437D-9E7D-108B145211A8}" presName="root2" presStyleCnt="0"/>
@@ -12234,6 +12484,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{71891B3C-826C-4756-A9BA-14E596B8A4AD}" type="pres">
       <dgm:prSet presAssocID="{8B7301AD-5D0D-437D-9E7D-108B145211A8}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12242,10 +12499,24 @@
     <dgm:pt modelId="{D435C461-2B81-4B82-B114-76B56B6019A5}" type="pres">
       <dgm:prSet presAssocID="{AC02D027-B653-4B77-A361-66C1E1D7CA50}" presName="conn2-1" presStyleLbl="parChTrans1D4" presStyleIdx="3" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{318B42E5-770F-472D-ACC9-D1A6704BADAE}" type="pres">
       <dgm:prSet presAssocID="{AC02D027-B653-4B77-A361-66C1E1D7CA50}" presName="connTx" presStyleLbl="parChTrans1D4" presStyleIdx="3" presStyleCnt="4"/>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{73614549-27F9-437F-BC45-9989DB391E62}" type="pres">
       <dgm:prSet presAssocID="{CFEB4CDE-F0B5-4022-AB14-10D7A3BD425B}" presName="root2" presStyleCnt="0"/>
@@ -12258,6 +12529,13 @@
         </dgm:presLayoutVars>
       </dgm:prSet>
       <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{9F347E03-D210-4419-A141-8E86578ADC41}" type="pres">
       <dgm:prSet presAssocID="{CFEB4CDE-F0B5-4022-AB14-10D7A3BD425B}" presName="level3hierChild" presStyleCnt="0"/>
@@ -12265,45 +12543,45 @@
     </dgm:pt>
   </dgm:ptLst>
   <dgm:cxnLst>
-    <dgm:cxn modelId="{3F84B703-CABE-44E6-B70D-56B8E90E557F}" type="presOf" srcId="{8B7301AD-5D0D-437D-9E7D-108B145211A8}" destId="{3E8CC95A-30BB-4288-A1FA-7394103B23E8}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E23C6F25-EBAB-4D8D-813E-9B443E08F072}" type="presOf" srcId="{36864AED-CFD1-4B11-9E77-829B0A685D8C}" destId="{1199E3A4-F43D-4B8D-9B92-9CCFF81D35F7}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8E9BF082-83F8-4427-B416-0F0A00D5DCF5}" type="presOf" srcId="{1C0ECF78-B8D5-495F-8B34-81D90F573DFC}" destId="{993821BC-5B4C-4351-A21C-51C3F561216C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{821CD031-D103-4C94-86A3-C6C23BF823DC}" type="presOf" srcId="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" destId="{B71EA1DC-AA5D-4DEF-AACD-D7B610C30043}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D4B4D20C-E54A-4A0F-8998-C59CE70A0654}" type="presOf" srcId="{9082B496-25FE-4169-9363-EAD41C1BAD0D}" destId="{D3A862F4-77FC-4D64-8A8A-38BAB036F2ED}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E6E3C997-6B60-4E00-92A1-B5963860F113}" srcId="{8B7301AD-5D0D-437D-9E7D-108B145211A8}" destId="{CFEB4CDE-F0B5-4022-AB14-10D7A3BD425B}" srcOrd="0" destOrd="0" parTransId="{AC02D027-B653-4B77-A361-66C1E1D7CA50}" sibTransId="{350C120B-5FD1-47A5-B158-69A7A418674E}"/>
+    <dgm:cxn modelId="{688C5CFB-4077-4602-8ECC-A7B0F4046EA4}" type="presOf" srcId="{CFEB4CDE-F0B5-4022-AB14-10D7A3BD425B}" destId="{7D3F564C-C748-4E8D-961D-03041E55C44F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B5425454-C44F-43DC-9F30-C4FDF837555D}" srcId="{75B7D391-4A29-41BC-9D59-8A7063971AAF}" destId="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" srcOrd="0" destOrd="0" parTransId="{B42D3CEC-CF6A-497B-BB12-1EA751780FEB}" sibTransId="{A7DD9B96-2E3C-4853-AA60-81CA5C4968F1}"/>
+    <dgm:cxn modelId="{D004069B-784F-4A7F-90F3-E3C14F8F8446}" type="presOf" srcId="{55C1839A-3EE2-469A-A968-C59B499D05BA}" destId="{B1487175-814D-407C-8DA0-5AF7332CCA9C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4702072B-957F-4FB0-91A5-5B66BA43F5A2}" srcId="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" destId="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" srcOrd="0" destOrd="0" parTransId="{36864AED-CFD1-4B11-9E77-829B0A685D8C}" sibTransId="{B4C11FAF-C878-4A33-8573-836E65739DA5}"/>
     <dgm:cxn modelId="{597DA304-403F-4755-BB62-78551B02FF74}" type="presOf" srcId="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" destId="{7AD7728E-1E11-48A9-A67A-2806F1343BF8}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{43F1770C-4109-4EF3-952E-854312585866}" srcId="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" destId="{0914DEFE-6C17-444F-A152-4ADFA2A76D26}" srcOrd="1" destOrd="0" parTransId="{55C1839A-3EE2-469A-A968-C59B499D05BA}" sibTransId="{A324E984-6FD7-4A91-A65E-95BF4B8D8819}"/>
-    <dgm:cxn modelId="{D4B4D20C-E54A-4A0F-8998-C59CE70A0654}" type="presOf" srcId="{9082B496-25FE-4169-9363-EAD41C1BAD0D}" destId="{D3A862F4-77FC-4D64-8A8A-38BAB036F2ED}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{E23C6F25-EBAB-4D8D-813E-9B443E08F072}" type="presOf" srcId="{36864AED-CFD1-4B11-9E77-829B0A685D8C}" destId="{1199E3A4-F43D-4B8D-9B92-9CCFF81D35F7}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{4702072B-957F-4FB0-91A5-5B66BA43F5A2}" srcId="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" destId="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" srcOrd="0" destOrd="0" parTransId="{36864AED-CFD1-4B11-9E77-829B0A685D8C}" sibTransId="{B4C11FAF-C878-4A33-8573-836E65739DA5}"/>
-    <dgm:cxn modelId="{81B84F2B-AAF3-4D0C-9682-3A9EE579370D}" type="presOf" srcId="{A025D5F7-5B4B-4020-AB63-5C964A5C6026}" destId="{4BC60D47-C429-461D-86FB-7B0D10F0C78D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{821CD031-D103-4C94-86A3-C6C23BF823DC}" type="presOf" srcId="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" destId="{B71EA1DC-AA5D-4DEF-AACD-D7B610C30043}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{D6706D34-8E4B-428E-9F34-F18633DF773E}" type="presOf" srcId="{E4A990BC-AF9F-4844-9083-823B3AD7C5C2}" destId="{C2813F44-1BCE-4CF0-A191-6A9BA88049E6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{5FA74239-E1AA-47A6-86BE-C83F566EFDA9}" srcId="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" destId="{C6A1D183-7FF4-4FAE-B98F-BC54AB628D5A}" srcOrd="1" destOrd="0" parTransId="{A025D5F7-5B4B-4020-AB63-5C964A5C6026}" sibTransId="{BCFC3C59-907B-437F-89F0-1BFE6A288355}"/>
-    <dgm:cxn modelId="{A8F98E61-DB01-419C-925A-4AFB27DE3123}" type="presOf" srcId="{E4A990BC-AF9F-4844-9083-823B3AD7C5C2}" destId="{AD1E0002-1710-4BA8-9A2D-4BE914CC023A}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{E515E243-A81E-4C9A-AC48-53641A22A375}" type="presOf" srcId="{B04B3A0E-FD10-45FE-A5E2-BCCFAF03BAF1}" destId="{B7C4DFC0-44F7-47C9-A480-3B14710B7086}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{A651436A-A901-44B6-9405-2C3194C6719F}" srcId="{C6A1D183-7FF4-4FAE-B98F-BC54AB628D5A}" destId="{8B7301AD-5D0D-437D-9E7D-108B145211A8}" srcOrd="0" destOrd="0" parTransId="{B04B3A0E-FD10-45FE-A5E2-BCCFAF03BAF1}" sibTransId="{D4CBB90B-7089-40DB-8648-F6865918F443}"/>
-    <dgm:cxn modelId="{70F19570-1A9F-4E31-84F8-DE8FB47CC1D5}" type="presOf" srcId="{1C0ECF78-B8D5-495F-8B34-81D90F573DFC}" destId="{D513FF87-3C30-4322-BFFA-C63F22E86710}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{0F619D70-1841-4050-AE82-E0AA0F83B08D}" type="presOf" srcId="{A025D5F7-5B4B-4020-AB63-5C964A5C6026}" destId="{EFA5B1EC-EF2F-43C8-B9F3-3110BC769A18}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{B5425454-C44F-43DC-9F30-C4FDF837555D}" srcId="{75B7D391-4A29-41BC-9D59-8A7063971AAF}" destId="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" srcOrd="0" destOrd="0" parTransId="{B42D3CEC-CF6A-497B-BB12-1EA751780FEB}" sibTransId="{A7DD9B96-2E3C-4853-AA60-81CA5C4968F1}"/>
-    <dgm:cxn modelId="{23C36A56-D7BE-4BB9-A3FF-19CEB3E7A7A2}" type="presOf" srcId="{55C1839A-3EE2-469A-A968-C59B499D05BA}" destId="{B8B595D4-1AA7-4313-8314-007ECD9CDB77}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{8E9BF082-83F8-4427-B416-0F0A00D5DCF5}" type="presOf" srcId="{1C0ECF78-B8D5-495F-8B34-81D90F573DFC}" destId="{993821BC-5B4C-4351-A21C-51C3F561216C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{84A82993-07E2-4A42-A996-46900583FFD5}" type="presOf" srcId="{C9B97DA7-12E3-4241-8F63-104B4ECBB5A4}" destId="{C2D3945D-4E06-4CA2-AF42-3C456595FA60}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{E6E3C997-6B60-4E00-92A1-B5963860F113}" srcId="{8B7301AD-5D0D-437D-9E7D-108B145211A8}" destId="{CFEB4CDE-F0B5-4022-AB14-10D7A3BD425B}" srcOrd="0" destOrd="0" parTransId="{AC02D027-B653-4B77-A361-66C1E1D7CA50}" sibTransId="{350C120B-5FD1-47A5-B158-69A7A418674E}"/>
-    <dgm:cxn modelId="{D004069B-784F-4A7F-90F3-E3C14F8F8446}" type="presOf" srcId="{55C1839A-3EE2-469A-A968-C59B499D05BA}" destId="{B1487175-814D-407C-8DA0-5AF7332CCA9C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{9A6196A8-A767-498B-9EE4-E2E6CD9FDBF2}" type="presOf" srcId="{36864AED-CFD1-4B11-9E77-829B0A685D8C}" destId="{FA110F8D-A383-48E7-9886-D97D3E84D77B}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{5842ECA9-F746-4C0A-A705-5FD8D552C0A2}" type="presOf" srcId="{31D6180F-ECE4-4AAC-88E5-C9AF6894F914}" destId="{F29B6492-ADF9-462F-8B22-062289126E4B}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{2B8320AD-B5F0-4C10-9D29-1AE058F78511}" type="presOf" srcId="{B04B3A0E-FD10-45FE-A5E2-BCCFAF03BAF1}" destId="{D6282B98-BD3A-41BF-943D-112DAAE6E3D3}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{68980EAF-F4E0-4134-9C02-831E8055E13F}" type="presOf" srcId="{1A01BAB7-D852-42EC-A523-3E0FC524173A}" destId="{1E4F17B2-61C1-4211-9112-21EAEF2D66DE}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{4F59CCAF-7129-4B54-A4FE-70DB32A1AB06}" type="presOf" srcId="{C5672A87-218B-4E36-BC10-7ABBD4A208F8}" destId="{642034F3-0EE3-4AA1-9236-83102005B437}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{FA7F50BC-A085-4985-B529-E11AA629042B}" type="presOf" srcId="{0914DEFE-6C17-444F-A152-4ADFA2A76D26}" destId="{B383E499-EC4E-4EDC-99D9-35F698E47E93}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{CC9C15C0-2070-4F20-BDF5-6712228E4B64}" srcId="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" destId="{C5672A87-218B-4E36-BC10-7ABBD4A208F8}" srcOrd="0" destOrd="0" parTransId="{9082B496-25FE-4169-9363-EAD41C1BAD0D}" sibTransId="{86CFA9BB-6233-4B86-9BD4-4D1A8250F711}"/>
-    <dgm:cxn modelId="{DD81C8C0-F814-4A71-B178-26C38485AB03}" type="presOf" srcId="{75B7D391-4A29-41BC-9D59-8A7063971AAF}" destId="{3789F7D8-6AC4-4DF3-B8E5-636A17DD51FD}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{6FF2E9C2-7411-471F-B7B4-1B3B5C0C18DB}" type="presOf" srcId="{AC02D027-B653-4B77-A361-66C1E1D7CA50}" destId="{318B42E5-770F-472D-ACC9-D1A6704BADAE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{B2C0DAC4-923B-4605-B76F-E8E31B5A2F4C}" srcId="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" destId="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" srcOrd="0" destOrd="0" parTransId="{1A01BAB7-D852-42EC-A523-3E0FC524173A}" sibTransId="{526E5ED3-9EBC-4DD4-9059-2BD77BA27ED4}"/>
-    <dgm:cxn modelId="{22463FC8-5B58-4793-AA67-633DA645D0DA}" type="presOf" srcId="{1A01BAB7-D852-42EC-A523-3E0FC524173A}" destId="{A6B5AC58-8480-4DD8-9BC5-CDFC9B0E3773}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{27FD6FCC-4B0E-4856-A61D-80EB9344E038}" type="presOf" srcId="{9082B496-25FE-4169-9363-EAD41C1BAD0D}" destId="{D74353A1-7855-41D7-BD9C-12C9D6E144B7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{8F2BA4CC-2A89-49E5-BA7F-60D3C868D503}" type="presOf" srcId="{C6A1D183-7FF4-4FAE-B98F-BC54AB628D5A}" destId="{F3E51841-17EC-4320-AF2E-2B9ED4FDE1EA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{D1EB92D1-4F82-44B2-8916-022EFA15D4A0}" srcId="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" destId="{C9B97DA7-12E3-4241-8F63-104B4ECBB5A4}" srcOrd="1" destOrd="0" parTransId="{1C0ECF78-B8D5-495F-8B34-81D90F573DFC}" sibTransId="{14C04757-3BF3-4BFA-9ED7-DCBE0F7B91E9}"/>
     <dgm:cxn modelId="{772E87E4-19D0-4434-A665-9F400A3B0D41}" type="presOf" srcId="{AC02D027-B653-4B77-A361-66C1E1D7CA50}" destId="{D435C461-2B81-4B82-B114-76B56B6019A5}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4F59CCAF-7129-4B54-A4FE-70DB32A1AB06}" type="presOf" srcId="{C5672A87-218B-4E36-BC10-7ABBD4A208F8}" destId="{642034F3-0EE3-4AA1-9236-83102005B437}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{27FD6FCC-4B0E-4856-A61D-80EB9344E038}" type="presOf" srcId="{9082B496-25FE-4169-9363-EAD41C1BAD0D}" destId="{D74353A1-7855-41D7-BD9C-12C9D6E144B7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{5842ECA9-F746-4C0A-A705-5FD8D552C0A2}" type="presOf" srcId="{31D6180F-ECE4-4AAC-88E5-C9AF6894F914}" destId="{F29B6492-ADF9-462F-8B22-062289126E4B}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{43F1770C-4109-4EF3-952E-854312585866}" srcId="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" destId="{0914DEFE-6C17-444F-A152-4ADFA2A76D26}" srcOrd="1" destOrd="0" parTransId="{55C1839A-3EE2-469A-A968-C59B499D05BA}" sibTransId="{A324E984-6FD7-4A91-A65E-95BF4B8D8819}"/>
+    <dgm:cxn modelId="{2B8320AD-B5F0-4C10-9D29-1AE058F78511}" type="presOf" srcId="{B04B3A0E-FD10-45FE-A5E2-BCCFAF03BAF1}" destId="{D6282B98-BD3A-41BF-943D-112DAAE6E3D3}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6FF2E9C2-7411-471F-B7B4-1B3B5C0C18DB}" type="presOf" srcId="{AC02D027-B653-4B77-A361-66C1E1D7CA50}" destId="{318B42E5-770F-472D-ACC9-D1A6704BADAE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{23C36A56-D7BE-4BB9-A3FF-19CEB3E7A7A2}" type="presOf" srcId="{55C1839A-3EE2-469A-A968-C59B499D05BA}" destId="{B8B595D4-1AA7-4313-8314-007ECD9CDB77}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{22463FC8-5B58-4793-AA67-633DA645D0DA}" type="presOf" srcId="{1A01BAB7-D852-42EC-A523-3E0FC524173A}" destId="{A6B5AC58-8480-4DD8-9BC5-CDFC9B0E3773}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{5FA74239-E1AA-47A6-86BE-C83F566EFDA9}" srcId="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" destId="{C6A1D183-7FF4-4FAE-B98F-BC54AB628D5A}" srcOrd="1" destOrd="0" parTransId="{A025D5F7-5B4B-4020-AB63-5C964A5C6026}" sibTransId="{BCFC3C59-907B-437F-89F0-1BFE6A288355}"/>
+    <dgm:cxn modelId="{FA7F50BC-A085-4985-B529-E11AA629042B}" type="presOf" srcId="{0914DEFE-6C17-444F-A152-4ADFA2A76D26}" destId="{B383E499-EC4E-4EDC-99D9-35F698E47E93}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D6706D34-8E4B-428E-9F34-F18633DF773E}" type="presOf" srcId="{E4A990BC-AF9F-4844-9083-823B3AD7C5C2}" destId="{C2813F44-1BCE-4CF0-A191-6A9BA88049E6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{70F19570-1A9F-4E31-84F8-DE8FB47CC1D5}" type="presOf" srcId="{1C0ECF78-B8D5-495F-8B34-81D90F573DFC}" destId="{D513FF87-3C30-4322-BFFA-C63F22E86710}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E515E243-A81E-4C9A-AC48-53641A22A375}" type="presOf" srcId="{B04B3A0E-FD10-45FE-A5E2-BCCFAF03BAF1}" destId="{B7C4DFC0-44F7-47C9-A480-3B14710B7086}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A8F98E61-DB01-419C-925A-4AFB27DE3123}" type="presOf" srcId="{E4A990BC-AF9F-4844-9083-823B3AD7C5C2}" destId="{AD1E0002-1710-4BA8-9A2D-4BE914CC023A}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CC9C15C0-2070-4F20-BDF5-6712228E4B64}" srcId="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" destId="{C5672A87-218B-4E36-BC10-7ABBD4A208F8}" srcOrd="0" destOrd="0" parTransId="{9082B496-25FE-4169-9363-EAD41C1BAD0D}" sibTransId="{86CFA9BB-6233-4B86-9BD4-4D1A8250F711}"/>
+    <dgm:cxn modelId="{68980EAF-F4E0-4134-9C02-831E8055E13F}" type="presOf" srcId="{1A01BAB7-D852-42EC-A523-3E0FC524173A}" destId="{1E4F17B2-61C1-4211-9112-21EAEF2D66DE}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1F76F3FC-4CFA-4B4F-A0B4-7B2D4A5CA65F}" type="presOf" srcId="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" destId="{765BCC75-F323-4F23-9E4F-05AF23F1A45D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{DD81C8C0-F814-4A71-B178-26C38485AB03}" type="presOf" srcId="{75B7D391-4A29-41BC-9D59-8A7063971AAF}" destId="{3789F7D8-6AC4-4DF3-B8E5-636A17DD51FD}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{81B84F2B-AAF3-4D0C-9682-3A9EE579370D}" type="presOf" srcId="{A025D5F7-5B4B-4020-AB63-5C964A5C6026}" destId="{4BC60D47-C429-461D-86FB-7B0D10F0C78D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{8085CAF9-53C3-4A2C-9A41-CD1BD9B4D669}" srcId="{0914DEFE-6C17-444F-A152-4ADFA2A76D26}" destId="{31D6180F-ECE4-4AAC-88E5-C9AF6894F914}" srcOrd="0" destOrd="0" parTransId="{E4A990BC-AF9F-4844-9083-823B3AD7C5C2}" sibTransId="{E21CD831-1C61-49A1-825C-F4960A7218FF}"/>
-    <dgm:cxn modelId="{688C5CFB-4077-4602-8ECC-A7B0F4046EA4}" type="presOf" srcId="{CFEB4CDE-F0B5-4022-AB14-10D7A3BD425B}" destId="{7D3F564C-C748-4E8D-961D-03041E55C44F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
-    <dgm:cxn modelId="{1F76F3FC-4CFA-4B4F-A0B4-7B2D4A5CA65F}" type="presOf" srcId="{C3C4AD0C-8D93-4517-99A6-7BB2DE6CEC04}" destId="{765BCC75-F323-4F23-9E4F-05AF23F1A45D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B2C0DAC4-923B-4605-B76F-E8E31B5A2F4C}" srcId="{DF4EB251-91B0-4EDC-A30F-364A10D62192}" destId="{E305F6E0-EC7F-461D-B1AD-D138B59A1146}" srcOrd="0" destOrd="0" parTransId="{1A01BAB7-D852-42EC-A523-3E0FC524173A}" sibTransId="{526E5ED3-9EBC-4DD4-9059-2BD77BA27ED4}"/>
+    <dgm:cxn modelId="{A651436A-A901-44B6-9405-2C3194C6719F}" srcId="{C6A1D183-7FF4-4FAE-B98F-BC54AB628D5A}" destId="{8B7301AD-5D0D-437D-9E7D-108B145211A8}" srcOrd="0" destOrd="0" parTransId="{B04B3A0E-FD10-45FE-A5E2-BCCFAF03BAF1}" sibTransId="{D4CBB90B-7089-40DB-8648-F6865918F443}"/>
+    <dgm:cxn modelId="{3F84B703-CABE-44E6-B70D-56B8E90E557F}" type="presOf" srcId="{8B7301AD-5D0D-437D-9E7D-108B145211A8}" destId="{3E8CC95A-30BB-4288-A1FA-7394103B23E8}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9A6196A8-A767-498B-9EE4-E2E6CD9FDBF2}" type="presOf" srcId="{36864AED-CFD1-4B11-9E77-829B0A685D8C}" destId="{FA110F8D-A383-48E7-9886-D97D3E84D77B}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{0F619D70-1841-4050-AE82-E0AA0F83B08D}" type="presOf" srcId="{A025D5F7-5B4B-4020-AB63-5C964A5C6026}" destId="{EFA5B1EC-EF2F-43C8-B9F3-3110BC769A18}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8F2BA4CC-2A89-49E5-BA7F-60D3C868D503}" type="presOf" srcId="{C6A1D183-7FF4-4FAE-B98F-BC54AB628D5A}" destId="{F3E51841-17EC-4320-AF2E-2B9ED4FDE1EA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{C2C2D9A9-C18B-4814-96F3-BC5EB91C6053}" type="presParOf" srcId="{3789F7D8-6AC4-4DF3-B8E5-636A17DD51FD}" destId="{E47C858A-1874-4624-871F-0FF6CF740EFD}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{CF8469B5-754E-4710-86F6-1760171C5029}" type="presParOf" srcId="{E47C858A-1874-4624-871F-0FF6CF740EFD}" destId="{7AD7728E-1E11-48A9-A67A-2806F1343BF8}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{45522720-97E5-4877-B892-2691BCB8135F}" type="presParOf" srcId="{E47C858A-1874-4624-871F-0FF6CF740EFD}" destId="{6D5C6819-F805-4502-B02D-B89F900D7C7C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
@@ -12793,7 +13071,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="2889250">
+          <a:pPr lvl="0" algn="ctr" defTabSz="2889250">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -12803,7 +13081,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="6500" kern="1200"/>
@@ -12912,7 +13189,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -12922,7 +13199,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -13031,7 +13307,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13041,7 +13317,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -13150,7 +13425,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13160,7 +13435,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -13269,7 +13543,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13279,7 +13553,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -13360,7 +13633,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="1066800">
+          <a:pPr lvl="0" algn="ctr" defTabSz="1066800">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13370,7 +13643,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="2400" kern="1200"/>
@@ -13442,7 +13714,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13452,7 +13724,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -13518,7 +13789,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13528,7 +13799,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -13600,7 +13870,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13610,7 +13880,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -13676,7 +13945,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="889000">
+          <a:pPr lvl="0" algn="ctr" defTabSz="889000">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13686,7 +13955,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="2000" kern="1200"/>
@@ -13758,7 +14026,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13768,7 +14036,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -13834,7 +14101,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13844,7 +14111,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -13852,7 +14118,7 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13862,7 +14128,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -13934,7 +14199,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -13944,7 +14209,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -14010,7 +14274,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr lvl="0" algn="ctr" defTabSz="622300">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14020,7 +14284,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1400" kern="1200"/>
@@ -14028,7 +14291,7 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr lvl="0" algn="ctr" defTabSz="622300">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14038,7 +14301,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1400" kern="1200"/>
@@ -14046,7 +14308,7 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr lvl="0" algn="ctr" defTabSz="622300">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14056,7 +14318,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1400" kern="1200"/>
@@ -14128,7 +14389,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14138,7 +14399,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -14204,7 +14464,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="800100">
+          <a:pPr lvl="0" algn="ctr" defTabSz="800100">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14214,7 +14474,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1800" kern="1200"/>
@@ -14286,7 +14545,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14296,7 +14555,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -14362,7 +14620,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725">
+          <a:pPr lvl="0" algn="ctr" defTabSz="466725">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14372,7 +14630,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1050" kern="1200"/>
@@ -14380,7 +14637,7 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725">
+          <a:pPr lvl="0" algn="ctr" defTabSz="466725">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14390,7 +14647,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1050" kern="1200"/>
@@ -14398,7 +14654,7 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725">
+          <a:pPr lvl="0" algn="ctr" defTabSz="466725">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14408,7 +14664,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1050" kern="1200"/>
@@ -14416,7 +14671,7 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725">
+          <a:pPr lvl="0" algn="ctr" defTabSz="466725">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14426,7 +14681,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1050" kern="1200"/>
@@ -14498,7 +14752,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14508,7 +14762,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -14574,7 +14827,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14584,7 +14837,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -14656,7 +14908,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14666,7 +14918,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -14732,7 +14983,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="711200">
+          <a:pPr lvl="0" algn="ctr" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14742,7 +14993,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1600" kern="1200"/>
@@ -14814,7 +15064,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="400050">
+          <a:pPr lvl="0" algn="ctr" defTabSz="400050">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14824,7 +15074,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:endParaRPr lang="es-CO" sz="900" kern="1200"/>
         </a:p>
@@ -14890,7 +15139,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr lvl="0" algn="ctr" defTabSz="622300">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -14900,7 +15149,6 @@
             <a:spcAft>
               <a:spcPct val="35000"/>
             </a:spcAft>
-            <a:buNone/>
           </a:pPr>
           <a:r>
             <a:rPr lang="es-CO" sz="1400" kern="1200"/>
@@ -18919,6 +19167,16 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1800" b="1" u="sng" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t/>
+          </a:r>
           <a:br>
             <a:rPr lang="es-CO" sz="1800" b="1" u="sng" baseline="0">
               <a:solidFill>
@@ -19680,7 +19938,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Inicio"/>
@@ -19735,7 +19993,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="sales"/>
@@ -20356,7 +20614,7 @@
             <v>46076</v>
           </cell>
           <cell r="K2" t="str">
-            <v>04:36 p. m.</v>
+            <v>04:36 p. m.</v>
           </cell>
           <cell r="L2">
             <v>16000</v>
@@ -21675,16 +21933,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Gráfico3"/>
@@ -21729,7 +21987,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Gráfico1"/>
@@ -21793,7 +22051,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Gráfico1"/>
@@ -21840,7 +22098,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Edwin Torres" refreshedDate="44040.519693402777" createdVersion="5" refreshedVersion="6" minRefreshableVersion="3" recordCount="19" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Edwin Torres" refreshedDate="44040.519693402777" createdVersion="5" refreshedVersion="6" minRefreshableVersion="3" recordCount="19">
   <cacheSource type="worksheet">
     <worksheetSource name="Pasivos"/>
   </cacheSource>
@@ -21960,7 +22218,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Edwin Torres" refreshedDate="44053.819915509259" createdVersion="5" refreshedVersion="6" minRefreshableVersion="3" recordCount="214" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Edwin Torres" refreshedDate="44053.819915509259" createdVersion="5" refreshedVersion="6" minRefreshableVersion="3" recordCount="214">
   <cacheSource type="worksheet">
     <worksheetSource name="sales"/>
   </cacheSource>
@@ -28648,7 +28906,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0800-000000000000}" name="Tabla dinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabla dinámica1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B4:E24" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="18">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -28926,7 +29184,7 @@
     <dataField name="Valor" fld="5" baseField="0" baseItem="0" numFmtId="166"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="216">
+    <format dxfId="212">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="0" count="0" selected="0"/>
@@ -28935,7 +29193,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="215">
+    <format dxfId="211">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -28944,7 +29202,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="214">
+    <format dxfId="210">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -28952,18 +29210,6 @@
           </reference>
         </references>
       </pivotArea>
-    </format>
-    <format dxfId="213">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="212">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
-    </format>
-    <format dxfId="211">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
-    </format>
-    <format dxfId="210">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="209">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
@@ -28978,12 +29224,24 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="205">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="204">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="203">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
+    <format dxfId="202">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="201">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="204">
+    <format dxfId="200">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="203">
+    <format dxfId="199">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1" selected="0">
@@ -28998,7 +29256,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="202">
+    <format dxfId="198">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="0" count="2" selected="0">
@@ -29016,7 +29274,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="201">
+    <format dxfId="197">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1" selected="0">
@@ -29045,206 +29303,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000004000000}" name="Tabla dinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Figures" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="37">
-  <location ref="W2:AB3" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="24">
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
-      <items count="2">
-        <item x="1"/>
-        <item x="0"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0"/>
-    <pivotField name="Mes  de   análisis" axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
-      <items count="7">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
-        <item h="1" x="6"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="166" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="166" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="174" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="1">
-    <i>
-      <x v="1"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-  </colItems>
-  <dataFields count="5">
-    <dataField name=" Venta" fld="7" baseField="0" baseItem="0" numFmtId="167"/>
-    <dataField name="Promedio Venta" fld="7" subtotal="average" baseField="3" baseItem="0"/>
-    <dataField name=" Gastos" fld="10" baseField="0" baseItem="0"/>
-    <dataField name=" Rent. trabajo" fld="19" baseField="0" baseItem="0" numFmtId="174"/>
-    <dataField name="Prom.  Rent. Trabajo" fld="19" subtotal="average" baseField="3" baseItem="1"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="172">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="171">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="170">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="169">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="168">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="167">
-      <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="166">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="165">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="164">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="163">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="4" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium11" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="dateNewerThan" evalOrder="-1" id="1">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters>
-            <customFilter operator="greaterThan" val="43909"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000003000000}" name="Rentabilidad" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="78">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Rentabilidad" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="78">
   <location ref="AQ4:AT34" firstHeaderRow="1" firstDataRow="1" firstDataCol="3" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="24">
     <pivotField axis="axisRow" compact="0" numFmtId="14" outline="0" showAll="0" defaultSubtotal="0">
@@ -29813,7 +29872,7 @@
     <dataField name=" Gastos" fld="10" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="173">
+    <format dxfId="159">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29840,8 +29899,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000002000000}" name="Ventas" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="64">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Ventas" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="64">
   <location ref="AJ4:AM34" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="24">
     <pivotField axis="axisRow" compact="0" numFmtId="14" outline="0" showAll="0" defaultSubtotal="0">
@@ -30407,7 +30466,7 @@
     <dataField name=" Venta" fld="7" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="174">
+    <format dxfId="160">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -30443,8 +30502,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000001000000}" name="Tabla dinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="53">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabla dinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="53">
   <location ref="A4:E34" firstHeaderRow="0" firstDataRow="1" firstDataCol="3" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="24">
     <pivotField axis="axisRow" compact="0" numFmtId="14" outline="0" showAll="0" defaultSubtotal="0">
@@ -31022,7 +31081,7 @@
     <dataField name=" Gastos" fld="10" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="175">
+    <format dxfId="161">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -31038,8 +31097,207 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabla dinámica4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Figures" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="37">
+  <location ref="W2:AB3" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="24">
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
+      <items count="2">
+        <item x="1"/>
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0"/>
+    <pivotField name="Mes  de   análisis" axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
+      <items count="7">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="166" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="166" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="174" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="1">
+    <i>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+  </colItems>
+  <dataFields count="5">
+    <dataField name=" Venta" fld="7" baseField="0" baseItem="0" numFmtId="167"/>
+    <dataField name="Promedio Venta" fld="7" subtotal="average" baseField="3" baseItem="0"/>
+    <dataField name=" Gastos" fld="10" baseField="0" baseItem="0"/>
+    <dataField name=" Rent. trabajo" fld="19" baseField="0" baseItem="0" numFmtId="174"/>
+    <dataField name="Prom.  Rent. Trabajo" fld="19" subtotal="average" baseField="3" baseItem="1"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="171">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="170">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="169">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="168">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="167">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="166">
+      <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="165">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="164">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="163">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="162">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium11" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="dateNewerThan" evalOrder="-1" id="1">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters>
+            <customFilter operator="greaterThan" val="43909"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0C00-000006000000}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Día" colHeaderCaption="Semana">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Día" colHeaderCaption="Semana">
   <location ref="A3:AH12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="24">
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -31256,23 +31514,23 @@
     <dataField name="Suma de Venta" fld="7" baseField="4" baseItem="7"/>
   </dataFields>
   <formats count="36">
-    <format dxfId="96">
+    <format dxfId="66">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="95">
+    <format dxfId="65">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="94">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="93">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="92">
+    <format dxfId="62">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="3" selected="0">
@@ -31290,7 +31548,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="91">
+    <format dxfId="61">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="4" selected="0">
@@ -31308,7 +31566,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="90">
+    <format dxfId="60">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31323,7 +31581,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="89">
+    <format dxfId="59">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31333,7 +31591,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="88">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31342,7 +31600,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="87">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31351,7 +31609,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="86">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31360,7 +31618,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="85">
+    <format dxfId="55">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="16" selected="0">
@@ -31389,7 +31647,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="84">
+    <format dxfId="54">
       <pivotArea field="4" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4" count="3">
@@ -31400,7 +31658,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="83">
+    <format dxfId="53">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="2" selected="0">
@@ -31415,7 +31673,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="52">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="3">
@@ -31426,7 +31684,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="81">
+    <format dxfId="51">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="15" selected="0">
@@ -31454,10 +31712,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="80">
+    <format dxfId="50">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="49">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="4" selected="0">
@@ -31470,7 +31728,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="78">
+    <format dxfId="48">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31486,7 +31744,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="77">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="4">
@@ -31498,7 +31756,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="46">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31507,7 +31765,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="75">
+    <format dxfId="45">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="3" selected="0">
@@ -31519,7 +31777,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="44">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31532,7 +31790,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31541,7 +31799,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="42">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31551,7 +31809,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="41">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="6" selected="0">
@@ -31569,7 +31827,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="40">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="5" selected="0">
@@ -31589,7 +31847,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="39">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31601,7 +31859,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="38">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31614,7 +31872,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="37">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31630,7 +31888,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="36">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31642,7 +31900,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="65">
+    <format dxfId="35">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31654,7 +31912,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="34">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="4" selected="0">
@@ -31669,7 +31927,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="33">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="3" selected="0">
@@ -31687,7 +31945,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="32">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="4" selected="0">
@@ -31702,7 +31960,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="31">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -31729,7 +31987,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0C00-000005000000}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Día" colHeaderCaption="Semana">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Día" colHeaderCaption="Semana">
   <location ref="AO4:AP12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="24">
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -31823,16 +32081,16 @@
     <dataField name="Prom. Venta PE &amp; CP" fld="23" subtotal="average" baseField="4" baseItem="5"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="108">
+    <format dxfId="78">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="107">
+    <format dxfId="77">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="106">
+    <format dxfId="76">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="105">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31841,7 +32099,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="104">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31850,7 +32108,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="103">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31859,7 +32117,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="102">
+    <format dxfId="72">
       <pivotArea field="4" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4" count="3">
@@ -31870,7 +32128,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="101">
+    <format dxfId="71">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="3">
@@ -31881,10 +32139,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="100">
+    <format dxfId="70">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="99">
+    <format dxfId="69">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="4">
@@ -31896,7 +32154,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="98">
+    <format dxfId="68">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31905,7 +32163,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="97">
+    <format dxfId="67">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -31928,7 +32186,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaciónDeDatos_Tipo_día" xr10:uid="{00000000-0013-0000-FFFF-FFFF01000000}" sourceName="Tipo día">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="SegmentaciónDeDatos_Tipo_día" sourceName="Tipo día">
   <pivotTables>
     <pivotTable tabId="33" name="Tabla dinámica4"/>
     <pivotTable tabId="33" name="Tabla dinámica1"/>
@@ -31947,7 +32205,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaciónDeDatos_Mes" xr10:uid="{00000000-0013-0000-FFFF-FFFF02000000}" sourceName="Mes">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="SegmentaciónDeDatos_Mes" sourceName="Mes">
   <pivotTables>
     <pivotTable tabId="33" name="Tabla dinámica4"/>
     <pivotTable tabId="33" name="Tabla dinámica1"/>
@@ -31971,104 +32229,104 @@
 </file>
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Tipo día" xr10:uid="{00000000-0014-0000-FFFF-FFFF01000000}" cache="SegmentaciónDeDatos_Tipo_día" caption="            Tipo día" style="SlicerStyleLight3" rowHeight="241300"/>
-  <slicer name="Mes" xr10:uid="{00000000-0014-0000-FFFF-FFFF02000000}" cache="SegmentaciónDeDatos_Mes" caption="                  Mes" style="SlicerStyleLight3" rowHeight="241300"/>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <slicer name="Tipo día" cache="SegmentaciónDeDatos_Tipo_día" caption="            Tipo día" style="SlicerStyleLight3" rowHeight="241300"/>
+  <slicer name="Mes" cache="SegmentaciónDeDatos_Mes" caption="                  Mes" style="SlicerStyleLight3" rowHeight="241300"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="sales" displayName="sales" ref="B2:N122" totalsRowShown="0" headerRowDxfId="294">
-  <autoFilter ref="B2:N122" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="sales" displayName="sales" ref="B2:N122" totalsRowShown="0" headerRowDxfId="292">
+  <autoFilter ref="B2:N122"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="293">
+    <tableColumn id="1" name="Fecha" dataDxfId="291">
       <calculatedColumnFormula>[2]sales_BI!J2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Hora" dataDxfId="292">
+    <tableColumn id="25" name="Hora" dataDxfId="290">
       <calculatedColumnFormula>[2]sales_BI!$K$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo día" dataDxfId="291" totalsRowDxfId="290"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="nombre_producto" dataDxfId="289" totalsRowDxfId="288">
+    <tableColumn id="2" name="Tipo día" dataDxfId="289" totalsRowDxfId="288"/>
+    <tableColumn id="7" name="nombre_producto" dataDxfId="287" totalsRowDxfId="286">
       <calculatedColumnFormula>[2]sales!C5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="No. Semana de operación" dataDxfId="287" totalsRowDxfId="286" dataCellStyle="Millares [0]">
+    <tableColumn id="21" name="No. Semana de operación" dataDxfId="285" totalsRowDxfId="284" dataCellStyle="Millares [0]">
       <calculatedColumnFormula>+VLOOKUP(sales[[#This Row],[Fecha]],maestro!A:C,3,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{AD4F4B5B-76BC-4D6D-ACBC-358EA0AB45E3}" name="Gastos" dataDxfId="0" totalsRowDxfId="1" dataCellStyle="Millares [0]"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Tipo día2" dataDxfId="285" totalsRowDxfId="284">
+    <tableColumn id="8" name="Gastos" dataDxfId="283" totalsRowDxfId="282" dataCellStyle="Millares [0]"/>
+    <tableColumn id="10" name="Tipo día2" dataDxfId="281" totalsRowDxfId="280">
       <calculatedColumnFormula>+VLOOKUP(sales[[#This Row],[Fecha]],maestro!A:D,4,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Día" dataDxfId="283">
+    <tableColumn id="3" name="Día" dataDxfId="279">
       <calculatedColumnFormula>+TEXT(B3,"ddd")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Mes">
+    <tableColumn id="4" name="Mes">
       <calculatedColumnFormula>+TEXT(B3,"mmmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Margen de contribución" dataDxfId="282" totalsRowDxfId="281">
+    <tableColumn id="5" name="Margen de contribución" dataDxfId="278" totalsRowDxfId="277">
       <calculatedColumnFormula>+M3*0.35</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venta" dataDxfId="280" totalsRowDxfId="279">
+    <tableColumn id="6" name="Venta" dataDxfId="276" totalsRowDxfId="275">
       <calculatedColumnFormula>[2]sales_BI!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Caja" dataDxfId="278">
+    <tableColumn id="9" name="Caja" dataDxfId="274">
       <calculatedColumnFormula>[2]sales_BI!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Bancos" dataDxfId="277" totalsRowDxfId="276"/>
+    <tableColumn id="11" name="Bancos" dataDxfId="273" totalsRowDxfId="272"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Opex9" displayName="Opex9" ref="B1:U20" headerRowDxfId="60">
-  <autoFilter ref="B1:U20" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:Q9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Opex9" displayName="Opex9" ref="B1:U20" headerRowDxfId="30">
+  <autoFilter ref="B1:U20"/>
+  <sortState ref="B2:Q9">
     <sortCondition ref="B1:B9"/>
   </sortState>
   <tableColumns count="20">
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0900-000012000000}" name="Tipo" dataDxfId="59"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Fecha" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Mes" dataDxfId="56">
+    <tableColumn id="18" name="Tipo" dataDxfId="29"/>
+    <tableColumn id="1" name="Fecha" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="4" name="Mes" dataDxfId="26">
       <calculatedColumnFormula>+TEXT(C2,"mmmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="Arriendo" dataDxfId="55" totalsRowDxfId="54">
+    <tableColumn id="5" name="Arriendo" dataDxfId="25" totalsRowDxfId="24">
       <calculatedColumnFormula>+J2*0.3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="No. Días Arriendo" dataDxfId="53" totalsRowDxfId="52"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0900-000010000000}" name="Día Arriendo" dataDxfId="51" totalsRowDxfId="50">
+    <tableColumn id="14" name="No. Días Arriendo" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="16" name="Día Arriendo" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>IFERROR(Opex9[[#This Row],[Arriendo]]/Opex9[[#This Row],[No. Días Arriendo]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Gas" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="No. Días Gas" dataDxfId="47" totalsRowDxfId="46">
+    <tableColumn id="6" name="Gas" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="12" name="No. Días Gas" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>+F1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="Consumo (m3)" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0900-000011000000}" name="Costo prom. Gas" dataDxfId="43" totalsRowDxfId="42">
+    <tableColumn id="9" name="Consumo (m3)" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="17" name="Costo prom. Gas" dataDxfId="13" totalsRowDxfId="12">
       <calculatedColumnFormula>IFERROR(Opex9[[#This Row],[Gas]]/Opex9[[#This Row],[Consumo (m3)]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0900-000013000000}" name="Día Gas" dataDxfId="41">
+    <tableColumn id="19" name="Día Gas" dataDxfId="11">
       <calculatedColumnFormula>IFERROR(Opex9[[#This Row],[Gas]]/Opex9[[#This Row],[No. Días Arriendo]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Agua" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="Dìa Agua" dataDxfId="39">
+    <tableColumn id="3" name="Agua" dataDxfId="10"/>
+    <tableColumn id="7" name="Dìa Agua" dataDxfId="9">
       <calculatedColumnFormula>IFERROR(Opex9[[#This Row],[Agua]]/Opex9[[#This Row],[No. Días Arriendo]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="Energia" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Financiació Energia" dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="11" name="Energia" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Financiació Energia" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>'[4]Radicado Energia'!$C14</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0900-00000D000000}" name="No. Días Energia" dataDxfId="34">
+    <tableColumn id="13" name="No. Días Energia" dataDxfId="4">
       <calculatedColumnFormula>+X2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="Consumo_x000a_(KhW" dataDxfId="33"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0900-000014000000}" name="Costo prom. Energia" dataDxfId="32">
+    <tableColumn id="15" name="Consumo_x000a_(KhW" dataDxfId="3"/>
+    <tableColumn id="20" name="Costo prom. Energia" dataDxfId="2">
       <calculatedColumnFormula>IFERROR(Opex9[[#This Row],[Energia]]/Opex9[[#This Row],[Consumo
 (KhW]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="Fecha corte enega" dataDxfId="31">
+    <tableColumn id="8" name="Fecha corte enega" dataDxfId="1">
       <calculatedColumnFormula>+Opex9[[#This Row],[Arriendo]]-#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0900-000015000000}" name="Día Energia" dataDxfId="30" dataCellStyle="Millares [0]">
+    <tableColumn id="21" name="Día Energia" dataDxfId="0" dataCellStyle="Millares [0]">
       <calculatedColumnFormula>IFERROR(Opex9[[#This Row],[Energia]]/Opex9[[#This Row],[No. Días Arriendo]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -32077,94 +32335,94 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="sales2" displayName="sales2" ref="B2:N122" totalsRowShown="0" headerRowDxfId="275">
-  <autoFilter ref="B2:N122" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="sales2" displayName="sales2" ref="B2:N122" totalsRowShown="0" headerRowDxfId="271">
+  <autoFilter ref="B2:N122"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="274">
+    <tableColumn id="1" name="Fecha" dataDxfId="270">
       <calculatedColumnFormula>[2]sales_BI!J2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="dia_sem" dataDxfId="273">
+    <tableColumn id="2" name="dia_sem" dataDxfId="269">
       <calculatedColumnFormula>+TEXT(sales2[[#This Row],[Fecha]],"ddd")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Gastos" dataDxfId="272">
+    <tableColumn id="7" name="Gastos" dataDxfId="268">
       <calculatedColumnFormula>+sales2[[#This Row],[Arriendo]]+sales2[[#This Row],[Gas]]+sales2[[#This Row],[Agua]]+sales2[[#This Row],[Electricidad]]+sales2[[#This Row],[Nomina]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Arriendo" dataDxfId="271" totalsRowDxfId="270">
+    <tableColumn id="14" name="Arriendo" dataDxfId="267" totalsRowDxfId="266">
       <calculatedColumnFormula>+VLOOKUP(sales2[[#This Row],[Fecha]],Opex!C:J,8,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Servicios" dataDxfId="269" totalsRowDxfId="268">
+    <tableColumn id="3" name="Servicios" dataDxfId="265" totalsRowDxfId="264">
       <calculatedColumnFormula>+SUM(sales2[[#This Row],[Gas]:[Electricidad]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Gas" dataDxfId="267" totalsRowDxfId="266"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Agua" dataDxfId="265" totalsRowDxfId="264"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Internet" dataDxfId="263" totalsRowDxfId="262"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Electricidad" dataDxfId="261" totalsRowDxfId="260"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Nomina" dataDxfId="259" totalsRowDxfId="258"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Cajero" dataDxfId="257" totalsRowDxfId="256"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Parrillero" dataDxfId="255" totalsRowDxfId="254"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Domiciliario" dataDxfId="253" totalsRowDxfId="252"/>
+    <tableColumn id="16" name="Gas" dataDxfId="263" totalsRowDxfId="262"/>
+    <tableColumn id="13" name="Agua" dataDxfId="261" totalsRowDxfId="260"/>
+    <tableColumn id="5" name="Internet" dataDxfId="259" totalsRowDxfId="258"/>
+    <tableColumn id="12" name="Electricidad" dataDxfId="257" totalsRowDxfId="256"/>
+    <tableColumn id="17" name="Nomina" dataDxfId="255" totalsRowDxfId="254"/>
+    <tableColumn id="18" name="Cajero" dataDxfId="253" totalsRowDxfId="252"/>
+    <tableColumn id="15" name="Parrillero" dataDxfId="251" totalsRowDxfId="250"/>
+    <tableColumn id="19" name="Domiciliario" dataDxfId="249" totalsRowDxfId="248"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Opex" displayName="Opex" ref="B1:X13" headerRowDxfId="251">
-  <autoFilter ref="B1:X13" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:T9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Opex" displayName="Opex" ref="B1:X13" headerRowDxfId="247">
+  <autoFilter ref="B1:X13"/>
+  <sortState ref="C2:T9">
     <sortCondition ref="C1:C9"/>
   </sortState>
   <tableColumns count="23">
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="Tipo" dataDxfId="250"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="249" totalsRowDxfId="248"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0200-000017000000}" name="fecha_fin" dataDxfId="247" totalsRowDxfId="246"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Mes" dataDxfId="245">
+    <tableColumn id="18" name="Tipo" dataDxfId="246"/>
+    <tableColumn id="1" name="Fecha" dataDxfId="245" totalsRowDxfId="244"/>
+    <tableColumn id="23" name="fecha_fin" dataDxfId="243" totalsRowDxfId="242"/>
+    <tableColumn id="4" name="Mes" dataDxfId="241">
       <calculatedColumnFormula>+TEXT(C2,"mmmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Cuentas x Pagar" dataDxfId="244"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0200-000016000000}" name="Día C x P" dataDxfId="243">
+    <tableColumn id="10" name="Cuentas x Pagar" dataDxfId="240"/>
+    <tableColumn id="22" name="Día C x P" dataDxfId="239">
       <calculatedColumnFormula>+Opex[[#This Row],[Cuentas x Pagar]]/31</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Arriendo" dataDxfId="242" totalsRowDxfId="241">
+    <tableColumn id="5" name="Arriendo" dataDxfId="238" totalsRowDxfId="237">
       <calculatedColumnFormula>+M2*0.3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="No. Días Arriendo" dataDxfId="240" totalsRowDxfId="239">
+    <tableColumn id="14" name="No. Días Arriendo" dataDxfId="236" totalsRowDxfId="235">
       <calculatedColumnFormula>+Opex[[#This Row],[fecha_fin]]-Opex[[#This Row],[Fecha]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="Día Arriendo" dataDxfId="238" totalsRowDxfId="237">
+    <tableColumn id="16" name="Día Arriendo" dataDxfId="234" totalsRowDxfId="233">
       <calculatedColumnFormula>IFERROR(Opex[[#This Row],[Arriendo]]/Opex[[#This Row],[No. Días Arriendo]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Gas" dataDxfId="236" totalsRowDxfId="235"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="No. Días Gas" dataDxfId="234" totalsRowDxfId="233">
+    <tableColumn id="6" name="Gas" dataDxfId="232" totalsRowDxfId="231"/>
+    <tableColumn id="12" name="No. Días Gas" dataDxfId="230" totalsRowDxfId="229">
       <calculatedColumnFormula>+I1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Consumo (m3)" dataDxfId="232" totalsRowDxfId="231"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="Costo prom. Gas" dataDxfId="230" totalsRowDxfId="229">
+    <tableColumn id="9" name="Consumo (m3)" dataDxfId="228" totalsRowDxfId="227"/>
+    <tableColumn id="17" name="Costo prom. Gas" dataDxfId="226" totalsRowDxfId="225">
       <calculatedColumnFormula>IFERROR(Opex[[#This Row],[Gas]]/Opex[[#This Row],[Consumo (m3)]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0200-000013000000}" name="Día Gas" dataDxfId="228">
+    <tableColumn id="19" name="Día Gas" dataDxfId="224">
       <calculatedColumnFormula>IFERROR(Opex[[#This Row],[Gas]]/Opex[[#This Row],[No. Días Arriendo]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Agua" dataDxfId="227"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Dìa Agua" dataDxfId="226">
+    <tableColumn id="3" name="Agua" dataDxfId="223"/>
+    <tableColumn id="7" name="Dìa Agua" dataDxfId="222">
       <calculatedColumnFormula>IFERROR(Opex[[#This Row],[Agua]]/Opex[[#This Row],[No. Días Arriendo]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Energia" dataDxfId="225" totalsRowDxfId="224"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Financiació Energia" dataDxfId="223" totalsRowDxfId="222">
+    <tableColumn id="11" name="Energia" dataDxfId="221" totalsRowDxfId="220"/>
+    <tableColumn id="2" name="Financiació Energia" dataDxfId="219" totalsRowDxfId="218">
       <calculatedColumnFormula>'[4]Radicado Energia'!$C14</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="No. Días Energia" dataDxfId="221">
+    <tableColumn id="13" name="No. Días Energia" dataDxfId="217">
       <calculatedColumnFormula>+AA2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="Consumo_x000a_(KhW" dataDxfId="220"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0200-000014000000}" name="Costo prom. Energia" dataDxfId="219">
+    <tableColumn id="15" name="Consumo_x000a_(KhW" dataDxfId="216"/>
+    <tableColumn id="20" name="Costo prom. Energia" dataDxfId="215">
       <calculatedColumnFormula>IFERROR(Opex[[#This Row],[Energia]]/Opex[[#This Row],[Consumo
 (KhW]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Fecha corte enega" dataDxfId="218">
+    <tableColumn id="8" name="Fecha corte enega" dataDxfId="214">
       <calculatedColumnFormula>+Opex[[#This Row],[Arriendo]]-#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0200-000015000000}" name="Día Energia" dataDxfId="217" dataCellStyle="Millares [0]">
+    <tableColumn id="21" name="Día Energia" dataDxfId="213" dataCellStyle="Millares [0]">
       <calculatedColumnFormula>IFERROR(Opex[[#This Row],[Energia]]/Opex[[#This Row],[No. Días Arriendo]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -32173,112 +32431,112 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Planta_y_Equipo" displayName="Planta_y_Equipo" ref="B34:D56" totalsRowCount="1" headerRowDxfId="200">
-  <autoFilter ref="B34:D55" xr:uid="{00000000-0009-0000-0100-00000D000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:D42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Planta_y_Equipo" displayName="Planta_y_Equipo" ref="B34:D56" totalsRowCount="1" headerRowDxfId="196">
+  <autoFilter ref="B34:D55"/>
+  <sortState ref="B19:D42">
     <sortCondition descending="1" ref="D18:D42"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Inversion Proyecto" totalsRowLabel="Total"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Origen Equipo" dataDxfId="199" dataCellStyle="Millares"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Valor" totalsRowFunction="sum" dataDxfId="198" totalsRowDxfId="197" dataCellStyle="Millares"/>
+    <tableColumn id="1" name="Inversion Proyecto" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="Origen Equipo" dataDxfId="195" dataCellStyle="Millares"/>
+    <tableColumn id="3" name="Valor" totalsRowFunction="sum" dataDxfId="194" totalsRowDxfId="193" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Stock_Actual" displayName="Stock_Actual" ref="H34:I43" totalsRowCount="1" headerRowDxfId="196" dataDxfId="194" headerRowBorderDxfId="195" tableBorderDxfId="193" totalsRowBorderDxfId="192">
-  <autoFilter ref="H34:I42" xr:uid="{00000000-0009-0000-0100-00000E000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H25:I36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Stock_Actual" displayName="Stock_Actual" ref="H34:I43" totalsRowCount="1" headerRowDxfId="192" dataDxfId="190" headerRowBorderDxfId="191" tableBorderDxfId="189" totalsRowBorderDxfId="188">
+  <autoFilter ref="H34:I42"/>
+  <sortState ref="H25:I36">
     <sortCondition descending="1" ref="I19:I31"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Materia Prima" totalsRowLabel="Total" dataDxfId="191" totalsRowDxfId="190"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Valor" totalsRowFunction="sum" dataDxfId="189" totalsRowDxfId="188"/>
+    <tableColumn id="1" name="Materia Prima" totalsRowLabel="Total" dataDxfId="187" totalsRowDxfId="186"/>
+    <tableColumn id="2" name="Valor" totalsRowFunction="sum" dataDxfId="185" totalsRowDxfId="184"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Gastos_entrada" displayName="Gastos_entrada" ref="H4:I9" totalsRowCount="1" headerRowDxfId="187">
-  <autoFilter ref="H4:I8" xr:uid="{00000000-0009-0000-0100-00000F000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H5:I11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Gastos_entrada" displayName="Gastos_entrada" ref="H4:I9" totalsRowCount="1" headerRowDxfId="183">
+  <autoFilter ref="H4:I8"/>
+  <sortState ref="H5:I11">
     <sortCondition descending="1" ref="I2:I9"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Tipo de gasto" totalsRowLabel="Total"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Valor" totalsRowFunction="sum" dataDxfId="186" totalsRowDxfId="185" dataCellStyle="Millares"/>
+    <tableColumn id="1" name="Tipo de gasto" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="Valor" totalsRowFunction="sum" dataDxfId="182" totalsRowDxfId="181" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Stock_Ideal" displayName="Stock_Ideal" ref="H46:I54" totalsRowCount="1" headerRowDxfId="184" dataDxfId="182" headerRowBorderDxfId="183" tableBorderDxfId="181" totalsRowBorderDxfId="180">
-  <autoFilter ref="H46:I53" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H47:I53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Stock_Ideal" displayName="Stock_Ideal" ref="H46:I54" totalsRowCount="1" headerRowDxfId="180" dataDxfId="178" headerRowBorderDxfId="179" tableBorderDxfId="177" totalsRowBorderDxfId="176">
+  <autoFilter ref="H46:I53"/>
+  <sortState ref="H47:I53">
     <sortCondition descending="1" ref="I19:I31"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Materia Prima" totalsRowLabel="Total" dataDxfId="179" totalsRowDxfId="178"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Valor" totalsRowFunction="sum" dataDxfId="177" totalsRowDxfId="176"/>
+    <tableColumn id="1" name="Materia Prima" totalsRowLabel="Total" dataDxfId="175" totalsRowDxfId="174"/>
+    <tableColumn id="2" name="Valor" totalsRowFunction="sum" dataDxfId="173" totalsRowDxfId="172"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Pasivos" displayName="Pasivos" ref="A5:R25" totalsRowCount="1" headerRowDxfId="162" dataDxfId="160" totalsRowDxfId="158" headerRowBorderDxfId="161" tableBorderDxfId="159">
-  <autoFilter ref="A5:R24" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Pasivos" displayName="Pasivos" ref="A5:R25" totalsRowCount="1" headerRowDxfId="146" dataDxfId="144" totalsRowDxfId="142" headerRowBorderDxfId="145" tableBorderDxfId="143">
+  <autoFilter ref="A5:R24"/>
   <tableColumns count="18">
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Nombre proveedor" dataDxfId="157" totalsRowDxfId="156" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Proveedor" totalsRowLabel="Total" dataDxfId="155" totalsRowDxfId="154" dataCellStyle="Moneda 3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Tipo de obligación" dataDxfId="153" totalsRowDxfId="152" dataCellStyle="Moneda 3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Marzo" totalsRowFunction="sum" dataDxfId="151" totalsRowDxfId="150" dataCellStyle="Moneda 3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Valor pagado_x000a_Marzo" totalsRowFunction="custom" dataDxfId="149" totalsRowDxfId="148" dataCellStyle="Moneda">
+    <tableColumn id="5" name="Nombre proveedor" dataDxfId="141" totalsRowDxfId="140" dataCellStyle="Moneda"/>
+    <tableColumn id="7" name="Proveedor" totalsRowLabel="Total" dataDxfId="139" totalsRowDxfId="138" dataCellStyle="Moneda 3"/>
+    <tableColumn id="4" name="Tipo de obligación" dataDxfId="137" totalsRowDxfId="136" dataCellStyle="Moneda 3"/>
+    <tableColumn id="8" name="Marzo" totalsRowFunction="sum" dataDxfId="135" totalsRowDxfId="134" dataCellStyle="Moneda 3"/>
+    <tableColumn id="3" name="Valor pagado_x000a_Marzo" totalsRowFunction="custom" dataDxfId="133" totalsRowDxfId="132" dataCellStyle="Moneda">
       <totalsRowFormula>+SUM(Pasivos[Valor pagado
 Marzo])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Abril" totalsRowFunction="custom" dataDxfId="147" totalsRowDxfId="146" dataCellStyle="Moneda 3">
+    <tableColumn id="2" name="Abril" totalsRowFunction="custom" dataDxfId="131" totalsRowDxfId="130" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Abril])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Valor pagado_x000a_Abril" totalsRowFunction="custom" dataDxfId="145" totalsRowDxfId="144" dataCellStyle="Moneda 3">
+    <tableColumn id="1" name="Valor pagado_x000a_Abril" totalsRowFunction="custom" dataDxfId="129" totalsRowDxfId="128" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Valor pagado
 Abril])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Mayo" totalsRowFunction="custom" dataDxfId="143" totalsRowDxfId="142" dataCellStyle="Moneda 3">
+    <tableColumn id="12" name="Mayo" totalsRowFunction="custom" dataDxfId="127" totalsRowDxfId="126" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Mayo])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0700-00000D000000}" name="Valor pagado_x000a_Mayo" totalsRowFunction="custom" dataDxfId="141" totalsRowDxfId="140" dataCellStyle="Moneda 3">
+    <tableColumn id="13" name="Valor pagado_x000a_Mayo" totalsRowFunction="custom" dataDxfId="125" totalsRowDxfId="124" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Valor pagado
 Mayo])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Junio" totalsRowFunction="custom" dataDxfId="139" totalsRowDxfId="138" dataCellStyle="Moneda 3">
+    <tableColumn id="9" name="Junio" totalsRowFunction="custom" dataDxfId="123" totalsRowDxfId="122" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Junio])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Valor pagado_x000a_Junio" totalsRowFunction="custom" dataDxfId="137" totalsRowDxfId="136" dataCellStyle="Moneda 3">
+    <tableColumn id="14" name="Valor pagado_x000a_Junio" totalsRowFunction="custom" dataDxfId="121" totalsRowDxfId="120" dataCellStyle="Moneda 3">
       <calculatedColumnFormula>+Pasivos[[#This Row],[Junio]]</calculatedColumnFormula>
       <totalsRowFormula>+SUM(Pasivos[Valor pagado
 Junio])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Julio" totalsRowFunction="custom" dataDxfId="135" totalsRowDxfId="134" dataCellStyle="Moneda 3">
+    <tableColumn id="10" name="Julio" totalsRowFunction="custom" dataDxfId="119" totalsRowDxfId="118" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Julio])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="Pagos Julio x programar" totalsRowFunction="custom" dataDxfId="133" totalsRowDxfId="132" dataCellStyle="Moneda 3">
+    <tableColumn id="19" name="Pagos Julio x programar" totalsRowFunction="custom" dataDxfId="117" totalsRowDxfId="116" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Pagos Julio x programar])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="Valor pagado_x000a_Julio" totalsRowFunction="custom" dataDxfId="131" totalsRowDxfId="130" dataCellStyle="Moneda 3">
+    <tableColumn id="18" name="Valor pagado_x000a_Julio" totalsRowFunction="custom" dataDxfId="115" totalsRowDxfId="114" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Valor pagado
 Julio])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Valor por Pagar" totalsRowFunction="custom" dataDxfId="129" totalsRowDxfId="128" dataCellStyle="Moneda 3">
+    <tableColumn id="6" name="Valor por Pagar" totalsRowFunction="custom" dataDxfId="113" totalsRowDxfId="112" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos[Valor por Pagar])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Estado Tesoreria" dataDxfId="127" totalsRowDxfId="126" dataCellStyle="Moneda 3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Origen" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="Saldo nuevo admón" totalsRowFunction="custom" dataDxfId="123" totalsRowDxfId="122">
+    <tableColumn id="16" name="Estado Tesoreria" dataDxfId="111" totalsRowDxfId="110" dataCellStyle="Moneda 3"/>
+    <tableColumn id="11" name="Origen" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="15" name="Saldo nuevo admón" totalsRowFunction="custom" dataDxfId="107" totalsRowDxfId="106">
       <calculatedColumnFormula>+Pasivos[[#This Row],[Julio]]</calculatedColumnFormula>
       <totalsRowFormula>+SUM(Pasivos[Saldo nuevo admón])</totalsRowFormula>
     </tableColumn>
@@ -32288,13 +32546,13 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Pasivos8" displayName="Pasivos8" ref="A5:D8" totalsRowCount="1" headerRowDxfId="121" dataDxfId="119" totalsRowDxfId="117" headerRowBorderDxfId="120" tableBorderDxfId="118">
-  <autoFilter ref="A5:D7" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Pasivos8" displayName="Pasivos8" ref="A5:D8" totalsRowCount="1" headerRowDxfId="105" dataDxfId="103" totalsRowDxfId="101" headerRowBorderDxfId="104" tableBorderDxfId="102">
+  <autoFilter ref="A5:D7"/>
   <tableColumns count="4">
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="Proveedor" totalsRowLabel="Total" dataDxfId="116" totalsRowDxfId="115" dataCellStyle="Moneda"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Tipo de obligación" dataDxfId="114" totalsRowDxfId="113" dataCellStyle="Moneda 3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Nombre proveedor" dataDxfId="112" totalsRowDxfId="111" dataCellStyle="Moneda"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Junio" totalsRowFunction="custom" dataDxfId="110" totalsRowDxfId="109" dataCellStyle="Moneda 3">
+    <tableColumn id="7" name="Proveedor" totalsRowLabel="Total" dataDxfId="100" totalsRowDxfId="99" dataCellStyle="Moneda"/>
+    <tableColumn id="4" name="Tipo de obligación" dataDxfId="98" totalsRowDxfId="97" dataCellStyle="Moneda 3"/>
+    <tableColumn id="5" name="Nombre proveedor" dataDxfId="96" totalsRowDxfId="95" dataCellStyle="Moneda"/>
+    <tableColumn id="9" name="Junio" totalsRowFunction="custom" dataDxfId="94" totalsRowDxfId="93" dataCellStyle="Moneda 3">
       <totalsRowFormula>+SUM(Pasivos8[Junio])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -32571,7 +32829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D314"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -37586,13 +37844,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D314" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D314"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
@@ -37840,12 +38098,12 @@
       <c r="W7" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="X7" s="273">
+      <c r="X7" s="279">
         <f>+SUBTOTAL(3,B5:B1048576)</f>
         <v>30</v>
       </c>
-      <c r="Y7" s="273"/>
-      <c r="Z7" s="273"/>
+      <c r="Y7" s="279"/>
+      <c r="Z7" s="279"/>
       <c r="AK7" s="28" t="s">
         <v>278</v>
       </c>
@@ -39110,7 +39368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Hoja12">
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
@@ -39185,20 +39443,20 @@
       <c r="Q4" s="12"/>
       <c r="R4" s="12"/>
       <c r="S4" s="12"/>
-      <c r="U4" s="274" t="s">
+      <c r="U4" s="280" t="s">
         <v>194</v>
       </c>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275"/>
-      <c r="X4" s="276"/>
-      <c r="Y4" s="274" t="s">
+      <c r="V4" s="281"/>
+      <c r="W4" s="281"/>
+      <c r="X4" s="282"/>
+      <c r="Y4" s="280" t="s">
         <v>215</v>
       </c>
-      <c r="Z4" s="275"/>
-      <c r="AA4" s="275"/>
-      <c r="AB4" s="275"/>
-      <c r="AC4" s="275"/>
-      <c r="AD4" s="276"/>
+      <c r="Z4" s="281"/>
+      <c r="AA4" s="281"/>
+      <c r="AB4" s="281"/>
+      <c r="AC4" s="281"/>
+      <c r="AD4" s="282"/>
     </row>
     <row r="5" spans="1:35" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A5" s="38" t="s">
@@ -40922,49 +41180,49 @@
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <conditionalFormatting sqref="P6:P24">
-    <cfRule type="containsText" dxfId="27" priority="9" operator="containsText" text="Urgente">
+    <cfRule type="containsText" dxfId="158" priority="9" operator="containsText" text="Urgente">
       <formula>NOT(ISERROR(SEARCH("Urgente",P6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="10" operator="containsText" text="Pagado">
+    <cfRule type="containsText" dxfId="157" priority="10" operator="containsText" text="Pagado">
       <formula>NOT(ISERROR(SEARCH("Pagado",P6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="11" operator="containsText" text="Congelado">
+    <cfRule type="containsText" dxfId="156" priority="11" operator="containsText" text="Congelado">
       <formula>NOT(ISERROR(SEARCH("Congelado",P6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="12" operator="containsText" text="corto">
+    <cfRule type="containsText" dxfId="155" priority="12" operator="containsText" text="corto">
       <formula>NOT(ISERROR(SEARCH("corto",P6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q11">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="Urgente">
+    <cfRule type="containsText" dxfId="154" priority="1" operator="containsText" text="Urgente">
       <formula>NOT(ISERROR(SEARCH("Urgente",Q11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="Pagado">
+    <cfRule type="containsText" dxfId="153" priority="2" operator="containsText" text="Pagado">
       <formula>NOT(ISERROR(SEARCH("Pagado",Q11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="Congelado">
+    <cfRule type="containsText" dxfId="152" priority="3" operator="containsText" text="Congelado">
       <formula>NOT(ISERROR(SEARCH("Congelado",Q11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="corto">
+    <cfRule type="containsText" dxfId="151" priority="4" operator="containsText" text="corto">
       <formula>NOT(ISERROR(SEARCH("corto",Q11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q23:Q24">
-    <cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="Urgente">
+    <cfRule type="containsText" dxfId="150" priority="5" operator="containsText" text="Urgente">
       <formula>NOT(ISERROR(SEARCH("Urgente",Q23)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="6" operator="containsText" text="Pagado">
+    <cfRule type="containsText" dxfId="149" priority="6" operator="containsText" text="Pagado">
       <formula>NOT(ISERROR(SEARCH("Pagado",Q23)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="Congelado">
+    <cfRule type="containsText" dxfId="148" priority="7" operator="containsText" text="Congelado">
       <formula>NOT(ISERROR(SEARCH("Congelado",Q23)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="8" operator="containsText" text="corto">
+    <cfRule type="containsText" dxfId="147" priority="8" operator="containsText" text="corto">
       <formula>NOT(ISERROR(SEARCH("corto",Q23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P6:P24" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P6:P24">
       <formula1>"Pagar Urgente, Pagar Otro mes,Congelado,Pagado,Financiero"</formula1>
     </dataValidation>
   </dataValidations>
@@ -40979,7 +41237,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
@@ -41077,7 +41335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -41121,16 +41379,16 @@
       <c r="AA1" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="AK1" s="277" t="s">
+      <c r="AK1" s="283" t="s">
         <v>196</v>
       </c>
-      <c r="AL1" s="277"/>
-      <c r="AM1" s="277"/>
-      <c r="AO1" s="277" t="s">
+      <c r="AL1" s="283"/>
+      <c r="AM1" s="283"/>
+      <c r="AO1" s="283" t="s">
         <v>383</v>
       </c>
-      <c r="AP1" s="277"/>
-      <c r="AQ1" s="277"/>
+      <c r="AP1" s="283"/>
+      <c r="AQ1" s="283"/>
     </row>
     <row r="2" spans="1:62" x14ac:dyDescent="0.2">
       <c r="AO2" s="29" t="s">
@@ -43964,58 +44222,58 @@
     <mergeCell ref="AO1:AQ1"/>
   </mergeCells>
   <conditionalFormatting sqref="B17:W20">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="11" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="14" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:W23">
-    <cfRule type="cellIs" dxfId="13" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="12" operator="greaterThan">
       <formula>0.4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="13" operator="lessThan">
       <formula>-0.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:W30">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="6" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:W33">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="86" priority="4" operator="greaterThan">
       <formula>0.4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="85" priority="5" operator="lessThan">
       <formula>-0.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:AC13">
-    <cfRule type="cellIs" dxfId="7" priority="35" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="84" priority="35" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="83" priority="36" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM12">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="82" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="2" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ5:AQ12">
-    <cfRule type="cellIs" dxfId="3" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="27" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="79" priority="28" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44024,7 +44282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -44096,7 +44354,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -45743,7 +46001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
@@ -45753,7 +46011,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
@@ -45763,7 +46021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B5:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -45820,15 +46078,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D8" r:id="rId1" location="/buscar-inscritos" display="https://linea.ccb.org.co/CertificadosElectronicosR/Index.html - /buscar-inscritos" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
-    <hyperlink ref="D12" r:id="rId2" xr:uid="{00000000-0004-0000-1100-000001000000}"/>
+    <hyperlink ref="D8" r:id="rId1" location="/buscar-inscritos" display="https://linea.ccb.org.co/CertificadosElectronicosR/Index.html - /buscar-inscritos"/>
+    <hyperlink ref="D12" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:K7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -45905,7 +46163,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFFA3"/>
   </sheetPr>
@@ -45991,7 +46249,7 @@
       </c>
       <c r="C3" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D3" s="28" t="s">
         <v>160</v>
@@ -46042,7 +46300,7 @@
       </c>
       <c r="C4" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>160</v>
@@ -46092,7 +46350,7 @@
       </c>
       <c r="C5" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D5" s="28" t="s">
         <v>160</v>
@@ -46142,7 +46400,7 @@
       </c>
       <c r="C6" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>160</v>
@@ -46192,7 +46450,7 @@
       </c>
       <c r="C7" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D7" s="28" t="s">
         <v>160</v>
@@ -46242,7 +46500,7 @@
       </c>
       <c r="C8" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>160</v>
@@ -46292,7 +46550,7 @@
       </c>
       <c r="C9" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>160</v>
@@ -46342,7 +46600,7 @@
       </c>
       <c r="C10" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>160</v>
@@ -46392,7 +46650,7 @@
       </c>
       <c r="C11" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>160</v>
@@ -46442,7 +46700,7 @@
       </c>
       <c r="C12" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D12" s="28" t="s">
         <v>160</v>
@@ -46492,7 +46750,7 @@
       </c>
       <c r="C13" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>160</v>
@@ -46542,7 +46800,7 @@
       </c>
       <c r="C14" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D14" s="28" t="s">
         <v>160</v>
@@ -46592,7 +46850,7 @@
       </c>
       <c r="C15" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D15" s="28" t="s">
         <v>160</v>
@@ -46643,7 +46901,7 @@
       </c>
       <c r="C16" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>160</v>
@@ -46693,7 +46951,7 @@
       </c>
       <c r="C17" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>160</v>
@@ -46743,7 +47001,7 @@
       </c>
       <c r="C18" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>160</v>
@@ -46793,7 +47051,7 @@
       </c>
       <c r="C19" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>160</v>
@@ -46843,7 +47101,7 @@
       </c>
       <c r="C20" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>160</v>
@@ -46893,7 +47151,7 @@
       </c>
       <c r="C21" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>160</v>
@@ -46943,7 +47201,7 @@
       </c>
       <c r="C22" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>160</v>
@@ -46993,7 +47251,7 @@
       </c>
       <c r="C23" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D23" s="28" t="s">
         <v>160</v>
@@ -47043,7 +47301,7 @@
       </c>
       <c r="C24" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>160</v>
@@ -47093,7 +47351,7 @@
       </c>
       <c r="C25" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D25" s="28" t="s">
         <v>160</v>
@@ -47143,7 +47401,7 @@
       </c>
       <c r="C26" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D26" s="28" t="s">
         <v>160</v>
@@ -47193,7 +47451,7 @@
       </c>
       <c r="C27" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D27" s="28" t="s">
         <v>160</v>
@@ -47243,7 +47501,7 @@
       </c>
       <c r="C28" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D28" s="28" t="s">
         <v>160</v>
@@ -47293,7 +47551,7 @@
       </c>
       <c r="C29" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>160</v>
@@ -47343,7 +47601,7 @@
       </c>
       <c r="C30" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D30" s="28" t="s">
         <v>160</v>
@@ -47393,7 +47651,7 @@
       </c>
       <c r="C31" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D31" s="28" t="s">
         <v>160</v>
@@ -47443,7 +47701,7 @@
       </c>
       <c r="C32" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D32" s="28" t="s">
         <v>160</v>
@@ -47493,7 +47751,7 @@
       </c>
       <c r="C33" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D33" s="28" t="s">
         <v>160</v>
@@ -47543,7 +47801,7 @@
       </c>
       <c r="C34" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>160</v>
@@ -47593,7 +47851,7 @@
       </c>
       <c r="C35" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D35" s="28" t="s">
         <v>160</v>
@@ -47643,7 +47901,7 @@
       </c>
       <c r="C36" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>160</v>
@@ -47693,7 +47951,7 @@
       </c>
       <c r="C37" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>160</v>
@@ -47743,7 +48001,7 @@
       </c>
       <c r="C38" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D38" s="28" t="s">
         <v>160</v>
@@ -47793,7 +48051,7 @@
       </c>
       <c r="C39" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D39" s="28" t="s">
         <v>160</v>
@@ -47843,7 +48101,7 @@
       </c>
       <c r="C40" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D40" s="28" t="s">
         <v>160</v>
@@ -47893,7 +48151,7 @@
       </c>
       <c r="C41" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D41" s="28" t="s">
         <v>160</v>
@@ -47946,7 +48204,7 @@
       </c>
       <c r="C42" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D42" s="28" t="s">
         <v>160</v>
@@ -47999,7 +48257,7 @@
       </c>
       <c r="C43" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D43" s="28" t="s">
         <v>160</v>
@@ -48052,7 +48310,7 @@
       </c>
       <c r="C44" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D44" s="28" t="s">
         <v>160</v>
@@ -48102,7 +48360,7 @@
       </c>
       <c r="C45" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D45" s="28" t="s">
         <v>160</v>
@@ -48152,7 +48410,7 @@
       </c>
       <c r="C46" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D46" s="28" t="s">
         <v>160</v>
@@ -48205,7 +48463,7 @@
       </c>
       <c r="C47" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D47" s="28" t="s">
         <v>160</v>
@@ -48255,7 +48513,7 @@
       </c>
       <c r="C48" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D48" s="28" t="s">
         <v>160</v>
@@ -48308,7 +48566,7 @@
       </c>
       <c r="C49" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D49" s="28" t="s">
         <v>160</v>
@@ -48364,7 +48622,7 @@
       </c>
       <c r="C50" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D50" s="28" t="s">
         <v>160</v>
@@ -48414,7 +48672,7 @@
       </c>
       <c r="C51" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D51" s="28" t="s">
         <v>160</v>
@@ -48464,7 +48722,7 @@
       </c>
       <c r="C52" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D52" s="28" t="s">
         <v>160</v>
@@ -48520,7 +48778,7 @@
       </c>
       <c r="C53" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D53" s="28" t="s">
         <v>160</v>
@@ -48576,7 +48834,7 @@
       </c>
       <c r="C54" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D54" s="28" t="s">
         <v>160</v>
@@ -48626,7 +48884,7 @@
       </c>
       <c r="C55" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D55" s="28" t="s">
         <v>160</v>
@@ -48676,7 +48934,7 @@
       </c>
       <c r="C56" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D56" s="28" t="s">
         <v>160</v>
@@ -48726,7 +48984,7 @@
       </c>
       <c r="C57" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D57" s="28" t="s">
         <v>160</v>
@@ -48776,7 +49034,7 @@
       </c>
       <c r="C58" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D58" s="28" t="s">
         <v>160</v>
@@ -48826,7 +49084,7 @@
       </c>
       <c r="C59" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D59" s="28" t="s">
         <v>160</v>
@@ -48876,7 +49134,7 @@
       </c>
       <c r="C60" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D60" s="28" t="s">
         <v>160</v>
@@ -48926,7 +49184,7 @@
       </c>
       <c r="C61" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D61" s="28" t="s">
         <v>160</v>
@@ -48976,7 +49234,7 @@
       </c>
       <c r="C62" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D62" s="28" t="s">
         <v>160</v>
@@ -49026,7 +49284,7 @@
       </c>
       <c r="C63" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D63" s="28" t="s">
         <v>160</v>
@@ -49076,7 +49334,7 @@
       </c>
       <c r="C64" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D64" s="28" t="s">
         <v>160</v>
@@ -49126,7 +49384,7 @@
       </c>
       <c r="C65" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D65" s="28" t="s">
         <v>160</v>
@@ -49176,7 +49434,7 @@
       </c>
       <c r="C66" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D66" s="28" t="s">
         <v>160</v>
@@ -49226,7 +49484,7 @@
       </c>
       <c r="C67" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D67" s="28" t="s">
         <v>160</v>
@@ -49276,7 +49534,7 @@
       </c>
       <c r="C68" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D68" s="28" t="s">
         <v>160</v>
@@ -49326,7 +49584,7 @@
       </c>
       <c r="C69" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D69" s="28" t="s">
         <v>160</v>
@@ -49376,7 +49634,7 @@
       </c>
       <c r="C70" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D70" s="28" t="s">
         <v>160</v>
@@ -49426,7 +49684,7 @@
       </c>
       <c r="C71" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D71" s="28" t="s">
         <v>160</v>
@@ -49476,7 +49734,7 @@
       </c>
       <c r="C72" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>160</v>
@@ -49526,7 +49784,7 @@
       </c>
       <c r="C73" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D73" s="28" t="s">
         <v>160</v>
@@ -49576,7 +49834,7 @@
       </c>
       <c r="C74" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>160</v>
@@ -49626,7 +49884,7 @@
       </c>
       <c r="C75" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D75" s="28" t="s">
         <v>160</v>
@@ -49676,7 +49934,7 @@
       </c>
       <c r="C76" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D76" s="28" t="s">
         <v>160</v>
@@ -49726,7 +49984,7 @@
       </c>
       <c r="C77" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>160</v>
@@ -49776,7 +50034,7 @@
       </c>
       <c r="C78" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D78" s="28" t="s">
         <v>160</v>
@@ -49826,7 +50084,7 @@
       </c>
       <c r="C79" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D79" s="28" t="s">
         <v>160</v>
@@ -49876,7 +50134,7 @@
       </c>
       <c r="C80" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D80" s="28" t="s">
         <v>160</v>
@@ -49926,7 +50184,7 @@
       </c>
       <c r="C81" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D81" s="28" t="s">
         <v>160</v>
@@ -49976,7 +50234,7 @@
       </c>
       <c r="C82" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D82" s="28" t="s">
         <v>160</v>
@@ -50026,7 +50284,7 @@
       </c>
       <c r="C83" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D83" s="28" t="s">
         <v>160</v>
@@ -50076,7 +50334,7 @@
       </c>
       <c r="C84" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D84" s="28" t="s">
         <v>160</v>
@@ -50126,7 +50384,7 @@
       </c>
       <c r="C85" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D85" s="28" t="s">
         <v>160</v>
@@ -50176,7 +50434,7 @@
       </c>
       <c r="C86" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D86" s="28" t="s">
         <v>160</v>
@@ -50226,7 +50484,7 @@
       </c>
       <c r="C87" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D87" s="28" t="s">
         <v>160</v>
@@ -50276,7 +50534,7 @@
       </c>
       <c r="C88" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D88" s="28" t="s">
         <v>160</v>
@@ -50326,7 +50584,7 @@
       </c>
       <c r="C89" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>160</v>
@@ -50376,7 +50634,7 @@
       </c>
       <c r="C90" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D90" s="28" t="s">
         <v>160</v>
@@ -50426,7 +50684,7 @@
       </c>
       <c r="C91" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D91" s="28" t="s">
         <v>160</v>
@@ -50476,7 +50734,7 @@
       </c>
       <c r="C92" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D92" s="28" t="s">
         <v>160</v>
@@ -50526,7 +50784,7 @@
       </c>
       <c r="C93" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D93" s="28" t="s">
         <v>160</v>
@@ -50576,7 +50834,7 @@
       </c>
       <c r="C94" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D94" s="28" t="s">
         <v>160</v>
@@ -50626,7 +50884,7 @@
       </c>
       <c r="C95" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D95" s="28" t="s">
         <v>160</v>
@@ -50679,7 +50937,7 @@
       </c>
       <c r="C96" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D96" s="28" t="s">
         <v>160</v>
@@ -50729,7 +50987,7 @@
       </c>
       <c r="C97" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D97" s="28" t="s">
         <v>160</v>
@@ -50779,7 +51037,7 @@
       </c>
       <c r="C98" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D98" s="28" t="s">
         <v>160</v>
@@ -50829,7 +51087,7 @@
       </c>
       <c r="C99" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D99" s="28" t="s">
         <v>160</v>
@@ -50879,7 +51137,7 @@
       </c>
       <c r="C100" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D100" s="28" t="s">
         <v>160</v>
@@ -50929,7 +51187,7 @@
       </c>
       <c r="C101" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D101" s="28" t="s">
         <v>160</v>
@@ -50979,7 +51237,7 @@
       </c>
       <c r="C102" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D102" s="28" t="s">
         <v>160</v>
@@ -51029,7 +51287,7 @@
       </c>
       <c r="C103" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D103" s="28" t="s">
         <v>160</v>
@@ -51079,7 +51337,7 @@
       </c>
       <c r="C104" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D104" s="28" t="s">
         <v>160</v>
@@ -51129,7 +51387,7 @@
       </c>
       <c r="C105" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D105" s="28" t="s">
         <v>160</v>
@@ -51179,7 +51437,7 @@
       </c>
       <c r="C106" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D106" s="28" t="s">
         <v>160</v>
@@ -51229,7 +51487,7 @@
       </c>
       <c r="C107" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D107" s="28" t="s">
         <v>160</v>
@@ -51279,7 +51537,7 @@
       </c>
       <c r="C108" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D108" s="28" t="s">
         <v>160</v>
@@ -51329,7 +51587,7 @@
       </c>
       <c r="C109" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D109" s="28" t="s">
         <v>160</v>
@@ -51356,8 +51614,8 @@
         <v>febrero</v>
       </c>
       <c r="K109" s="1">
-        <f t="shared" si="9"/>
-        <v>1050</v>
+        <f>+VLOOKUP(sales[[#This Row],[nombre_producto]],products!A:C,3,0)</f>
+        <v>1200</v>
       </c>
       <c r="L109" s="145">
         <f>[2]sales_BI!H108</f>
@@ -51379,7 +51637,7 @@
       </c>
       <c r="C110" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D110" s="28" t="s">
         <v>160</v>
@@ -51429,7 +51687,7 @@
       </c>
       <c r="C111" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D111" s="28" t="s">
         <v>160</v>
@@ -51479,7 +51737,7 @@
       </c>
       <c r="C112" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D112" s="28" t="s">
         <v>160</v>
@@ -51529,7 +51787,7 @@
       </c>
       <c r="C113" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D113" s="28" t="s">
         <v>160</v>
@@ -51579,7 +51837,7 @@
       </c>
       <c r="C114" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D114" s="28" t="s">
         <v>160</v>
@@ -51629,7 +51887,7 @@
       </c>
       <c r="C115" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D115" s="28" t="s">
         <v>160</v>
@@ -51679,7 +51937,7 @@
       </c>
       <c r="C116" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D116" s="28" t="s">
         <v>160</v>
@@ -51729,7 +51987,7 @@
       </c>
       <c r="C117" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D117" s="28" t="s">
         <v>160</v>
@@ -51779,7 +52037,7 @@
       </c>
       <c r="C118" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D118" s="28" t="s">
         <v>160</v>
@@ -51829,7 +52087,7 @@
       </c>
       <c r="C119" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D119" s="28" t="s">
         <v>160</v>
@@ -51879,7 +52137,7 @@
       </c>
       <c r="C120" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D120" s="28" t="s">
         <v>160</v>
@@ -51929,7 +52187,7 @@
       </c>
       <c r="C121" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D121" s="28" t="s">
         <v>160</v>
@@ -51979,7 +52237,7 @@
       </c>
       <c r="C122" s="28" t="str">
         <f>[2]sales_BI!$K$2</f>
-        <v>04:36 p. m.</v>
+        <v>04:36 p. m.</v>
       </c>
       <c r="D122" s="28" t="s">
         <v>160</v>
@@ -52030,10 +52288,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F3:G122">
-    <cfRule type="containsText" dxfId="29" priority="134" operator="containsText" text="D) Domingo">
+    <cfRule type="containsText" dxfId="294" priority="134" operator="containsText" text="D) Domingo">
       <formula>NOT(ISERROR(SEARCH("D) Domingo",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="135" operator="containsText" text="viernes">
+    <cfRule type="containsText" dxfId="293" priority="135" operator="containsText" text="viernes">
       <formula>NOT(ISERROR(SEARCH("viernes",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52046,7 +52304,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Hoja17"/>
   <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -52742,77 +53000,222 @@
       <c r="C45"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:H25" xr:uid="{00000000-0009-0000-0000-000013000000}"/>
+  <autoFilter ref="A6:H25"/>
   <hyperlinks>
-    <hyperlink ref="G1" r:id="rId1" location="Cundinamarca" xr:uid="{00000000-0004-0000-1300-000000000000}"/>
+    <hyperlink ref="G1" r:id="rId1" location="Cundinamarca"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFFA3"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="260" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="179" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="179" t="s">
+        <v>441</v>
+      </c>
+      <c r="C1" s="273" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="270" t="s">
         <v>425</v>
       </c>
-      <c r="B1">
+      <c r="B2" s="275">
+        <v>8000</v>
+      </c>
+      <c r="C2" s="274">
+        <f>3500+8000</f>
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="271" t="s">
+        <v>436</v>
+      </c>
+      <c r="B3" s="275">
+        <v>4500</v>
+      </c>
+      <c r="C3" s="274">
+        <v>2416.6666666666665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="271" t="s">
+        <v>430</v>
+      </c>
+      <c r="B4" s="275">
+        <v>3000</v>
+      </c>
+      <c r="C4" s="274">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="271" t="s">
+        <v>340</v>
+      </c>
+      <c r="B5" s="275">
+        <v>3000</v>
+      </c>
+      <c r="C5" s="274">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="270" t="s">
+        <v>431</v>
+      </c>
+      <c r="B6" s="275">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="274">
+        <v>1166.6666666666667</v>
+      </c>
+      <c r="F6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G6" s="272">
+        <v>33000</v>
+      </c>
+      <c r="H6">
+        <v>24</v>
+      </c>
+      <c r="I6" s="272">
+        <f t="shared" ref="I6:I8" si="0">+G6/H6</f>
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="271" t="s">
+        <v>432</v>
+      </c>
+      <c r="B7" s="275">
+        <v>4500</v>
+      </c>
+      <c r="C7" s="274">
         <v>3500</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="F7" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>427</v>
-      </c>
-      <c r="C5">
-        <v>33000</v>
-      </c>
-      <c r="D5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>426</v>
-      </c>
-      <c r="C6">
+      <c r="G7" s="272">
         <v>29000</v>
       </c>
-      <c r="D6">
+      <c r="H7">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="I7" s="272">
+        <f t="shared" si="0"/>
+        <v>2416.6666666666665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="271" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" s="275">
+        <v>35000</v>
+      </c>
+      <c r="C8" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F8" t="s">
         <v>428</v>
       </c>
-      <c r="C7">
+      <c r="G8" s="272">
         <v>35000</v>
       </c>
-      <c r="D7">
+      <c r="H8">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="I8" s="272">
+        <f t="shared" si="0"/>
+        <v>1166.6666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="270" t="s">
+        <v>434</v>
+      </c>
+      <c r="B9" s="275">
+        <v>25000</v>
+      </c>
+      <c r="C9" s="4">
+        <v>15000</v>
+      </c>
+      <c r="F9" t="s">
         <v>429</v>
       </c>
-      <c r="C8">
+      <c r="G9" s="272">
         <v>36000</v>
       </c>
-      <c r="D8">
+      <c r="H9">
         <v>30</v>
+      </c>
+      <c r="I9" s="272">
+        <f>+G9/H9</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="271" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10" s="275">
+        <v>2000</v>
+      </c>
+      <c r="C10" s="4">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="270" t="s">
+        <v>437</v>
+      </c>
+      <c r="B11" s="275">
+        <v>48000</v>
+      </c>
+      <c r="C11" s="4">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="271" t="s">
+        <v>438</v>
+      </c>
+      <c r="B12" s="275">
+        <v>70000</v>
+      </c>
+      <c r="C12" s="4">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="270" t="s">
+        <v>439</v>
+      </c>
+      <c r="B13" s="275">
+        <v>40000</v>
+      </c>
+      <c r="C13" s="4">
+        <v>25000</v>
       </c>
     </row>
   </sheetData>
@@ -52821,7 +53224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFFA3"/>
   </sheetPr>
@@ -57526,7 +57929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -57580,7 +57983,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
@@ -58716,7 +59119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -58774,7 +59177,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
@@ -58793,7 +59196,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
@@ -58880,7 +59283,7 @@
       <c r="I5" s="4">
         <v>1000000</v>
       </c>
-      <c r="K5" s="270">
+      <c r="K5" s="276">
         <f>+M4+M7</f>
         <v>29478519</v>
       </c>
@@ -58919,7 +59322,7 @@
         <f>550000/2</f>
         <v>275000</v>
       </c>
-      <c r="K6" s="271"/>
+      <c r="K6" s="277"/>
       <c r="L6" s="26" t="s">
         <v>207</v>
       </c>
@@ -58954,7 +59357,7 @@
       <c r="I7" s="22">
         <v>200000</v>
       </c>
-      <c r="K7" s="271"/>
+      <c r="K7" s="277"/>
       <c r="L7" s="93" t="s">
         <v>143</v>
       </c>
@@ -58997,7 +59400,7 @@
       <c r="I8" s="4">
         <v>100000</v>
       </c>
-      <c r="K8" s="271"/>
+      <c r="K8" s="277"/>
       <c r="L8" s="253" t="s">
         <v>400</v>
       </c>
@@ -59033,7 +59436,7 @@
         <f>SUBTOTAL(109,Gastos_entrada[Valor])</f>
         <v>1575000</v>
       </c>
-      <c r="K9" s="272"/>
+      <c r="K9" s="278"/>
       <c r="L9" s="253" t="s">
         <v>399</v>
       </c>
